--- a/util/report_vellore.xlsx
+++ b/util/report_vellore.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FFCS Data" sheetId="1" r:id="R9fc35fca98534dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FFCS Data" sheetId="1" r:id="Re4b7e09a8c044a80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -485,7 +485,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FFCSDataTable" displayName="FFCSDataTable" ref="A1:G146" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FFCSDataTable" displayName="FFCSDataTable" ref="A1:G179" headerRowCount="1" totalsRowCount="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="CODE"/>
     <x:tableColumn id="2" name="TITLE"/>
@@ -4015,10 +4015,769 @@
         <x:v>SHILPI GUPTA</x:v>
       </x:c>
     </x:row>
+    <x:row r="147" ht="15" hidden="0" customHeight="1">
+      <x:c r="A147" s="61" t="str">
+        <x:v>BITE404E</x:v>
+      </x:c>
+      <x:c r="B147" s="62" t="str">
+        <x:v>Object Oriented Analysis and Design</x:v>
+      </x:c>
+      <x:c r="C147" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D147" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E147" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F147" s="62" t="str">
+        <x:v>G1</x:v>
+      </x:c>
+      <x:c r="G147" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="15" hidden="0" customHeight="1">
+      <x:c r="A148" s="61" t="str">
+        <x:v>BITE404E</x:v>
+      </x:c>
+      <x:c r="B148" s="62" t="str">
+        <x:v>Object Oriented Analysis and Design</x:v>
+      </x:c>
+      <x:c r="C148" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D148" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E148" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F148" s="62" t="str">
+        <x:v>L55+L56</x:v>
+      </x:c>
+      <x:c r="G148" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="15" hidden="0" customHeight="1">
+      <x:c r="A149" s="61" t="str">
+        <x:v>BITE404E</x:v>
+      </x:c>
+      <x:c r="B149" s="62" t="str">
+        <x:v>Object Oriented Analysis and Design</x:v>
+      </x:c>
+      <x:c r="C149" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D149" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E149" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F149" s="62" t="str">
+        <x:v>G2</x:v>
+      </x:c>
+      <x:c r="G149" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="15" hidden="0" customHeight="1">
+      <x:c r="A150" s="61" t="str">
+        <x:v>BITE404E</x:v>
+      </x:c>
+      <x:c r="B150" s="62" t="str">
+        <x:v>Object Oriented Analysis and Design</x:v>
+      </x:c>
+      <x:c r="C150" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D150" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E150" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F150" s="62" t="str">
+        <x:v>L3+L4</x:v>
+      </x:c>
+      <x:c r="G150" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="15" hidden="0" customHeight="1">
+      <x:c r="A151" s="61" t="str">
+        <x:v>BITE404E</x:v>
+      </x:c>
+      <x:c r="B151" s="62" t="str">
+        <x:v>Object Oriented Analysis and Design</x:v>
+      </x:c>
+      <x:c r="C151" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D151" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E151" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F151" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G151" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="15" hidden="0" customHeight="1">
+      <x:c r="A152" s="61" t="str">
+        <x:v>BITE404E</x:v>
+      </x:c>
+      <x:c r="B152" s="62" t="str">
+        <x:v>Object Oriented Analysis and Design</x:v>
+      </x:c>
+      <x:c r="C152" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D152" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E152" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F152" s="62" t="str">
+        <x:v>L25+L26</x:v>
+      </x:c>
+      <x:c r="G152" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="15" hidden="0" customHeight="1">
+      <x:c r="A153" s="61" t="str">
+        <x:v>BITE311L</x:v>
+      </x:c>
+      <x:c r="B153" s="62" t="str">
+        <x:v>Human Computer Interaction</x:v>
+      </x:c>
+      <x:c r="C153" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D153" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E153" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F153" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G153" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="15" hidden="0" customHeight="1">
+      <x:c r="A154" s="61" t="str">
+        <x:v>BITE311L</x:v>
+      </x:c>
+      <x:c r="B154" s="62" t="str">
+        <x:v>Human Computer Interaction</x:v>
+      </x:c>
+      <x:c r="C154" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D154" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E154" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F154" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G154" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="15" hidden="0" customHeight="1">
+      <x:c r="A155" s="61" t="str">
+        <x:v>BITE312E</x:v>
+      </x:c>
+      <x:c r="B155" s="62" t="str">
+        <x:v>Data Mining</x:v>
+      </x:c>
+      <x:c r="C155" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D155" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E155" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F155" s="62" t="str">
+        <x:v>G1</x:v>
+      </x:c>
+      <x:c r="G155" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="15" hidden="0" customHeight="1">
+      <x:c r="A156" s="61" t="str">
+        <x:v>BITE312E</x:v>
+      </x:c>
+      <x:c r="B156" s="62" t="str">
+        <x:v>Data Mining</x:v>
+      </x:c>
+      <x:c r="C156" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D156" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E156" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F156" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G156" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="15" hidden="0" customHeight="1">
+      <x:c r="A157" s="61" t="str">
+        <x:v>BITE312E</x:v>
+      </x:c>
+      <x:c r="B157" s="62" t="str">
+        <x:v>Data Mining</x:v>
+      </x:c>
+      <x:c r="C157" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D157" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E157" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F157" s="62" t="str">
+        <x:v>G2</x:v>
+      </x:c>
+      <x:c r="G157" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="15" hidden="0" customHeight="1">
+      <x:c r="A158" s="61" t="str">
+        <x:v>BITE312E</x:v>
+      </x:c>
+      <x:c r="B158" s="62" t="str">
+        <x:v>Data Mining</x:v>
+      </x:c>
+      <x:c r="C158" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D158" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E158" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F158" s="62" t="str">
+        <x:v>L11+L12</x:v>
+      </x:c>
+      <x:c r="G158" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="15" hidden="0" customHeight="1">
+      <x:c r="A159" s="61" t="str">
+        <x:v>BITE312E</x:v>
+      </x:c>
+      <x:c r="B159" s="62" t="str">
+        <x:v>Data Mining</x:v>
+      </x:c>
+      <x:c r="C159" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D159" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E159" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F159" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G159" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="15" hidden="0" customHeight="1">
+      <x:c r="A160" s="61" t="str">
+        <x:v>BITE312E</x:v>
+      </x:c>
+      <x:c r="B160" s="62" t="str">
+        <x:v>Data Mining</x:v>
+      </x:c>
+      <x:c r="C160" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D160" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E160" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F160" s="62" t="str">
+        <x:v>L1+L2</x:v>
+      </x:c>
+      <x:c r="G160" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="15" hidden="0" customHeight="1">
+      <x:c r="A161" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B161" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C161" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D161" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E161" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F161" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G161" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="15" hidden="0" customHeight="1">
+      <x:c r="A162" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B162" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C162" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D162" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E162" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F162" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G162" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="15" hidden="0" customHeight="1">
+      <x:c r="A163" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B163" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C163" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D163" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E163" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F163" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G163" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="15" hidden="0" customHeight="1">
+      <x:c r="A164" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B164" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C164" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D164" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E164" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F164" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G164" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="15" hidden="0" customHeight="1">
+      <x:c r="A165" s="61" t="str">
+        <x:v>BITE405L</x:v>
+      </x:c>
+      <x:c r="B165" s="62" t="str">
+        <x:v>Soft Computing</x:v>
+      </x:c>
+      <x:c r="C165" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D165" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E165" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F165" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G165" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="15" hidden="0" customHeight="1">
+      <x:c r="A166" s="61" t="str">
+        <x:v>BITE405L</x:v>
+      </x:c>
+      <x:c r="B166" s="62" t="str">
+        <x:v>Soft Computing</x:v>
+      </x:c>
+      <x:c r="C166" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D166" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E166" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F166" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G166" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="15" hidden="0" customHeight="1">
+      <x:c r="A167" s="61" t="str">
+        <x:v>BITE409L</x:v>
+      </x:c>
+      <x:c r="B167" s="62" t="str">
+        <x:v>Mobile Application Development</x:v>
+      </x:c>
+      <x:c r="C167" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D167" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E167" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F167" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G167" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="15" hidden="0" customHeight="1">
+      <x:c r="A168" s="61" t="str">
+        <x:v>BITE409L</x:v>
+      </x:c>
+      <x:c r="B168" s="62" t="str">
+        <x:v>Mobile Application Development</x:v>
+      </x:c>
+      <x:c r="C168" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D168" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E168" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F168" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G168" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="15" hidden="0" customHeight="1">
+      <x:c r="A169" s="61" t="str">
+        <x:v>BITE410L</x:v>
+      </x:c>
+      <x:c r="B169" s="62" t="str">
+        <x:v>Machine Learning</x:v>
+      </x:c>
+      <x:c r="C169" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D169" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E169" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F169" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G169" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="15" hidden="0" customHeight="1">
+      <x:c r="A170" s="61" t="str">
+        <x:v>BITE410L</x:v>
+      </x:c>
+      <x:c r="B170" s="62" t="str">
+        <x:v>Machine Learning</x:v>
+      </x:c>
+      <x:c r="C170" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D170" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E170" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F170" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G170" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="15" hidden="0" customHeight="1">
+      <x:c r="A171" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B171" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C171" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D171" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E171" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F171" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G171" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="15" hidden="0" customHeight="1">
+      <x:c r="A172" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B172" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C172" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D172" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E172" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F172" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G172" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="15" hidden="0" customHeight="1">
+      <x:c r="A173" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B173" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C173" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D173" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E173" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F173" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G173" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="15" hidden="0" customHeight="1">
+      <x:c r="A174" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B174" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C174" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D174" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E174" s="62" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+      <x:c r="F174" s="62" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="G174" s="63" t="str">
+        <x:v>Not announced</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="15" hidden="0" customHeight="1">
+      <x:c r="A175" s="61" t="str">
+        <x:v>BITE301L</x:v>
+      </x:c>
+      <x:c r="B175" s="62" t="str">
+        <x:v>Computer Architecture and Organization</x:v>
+      </x:c>
+      <x:c r="C175" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D175" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E175" s="62" t="str">
+        <x:v>PRP426</x:v>
+      </x:c>
+      <x:c r="F175" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G175" s="63" t="str">
+        <x:v>KARPAGAM S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="15" hidden="0" customHeight="1">
+      <x:c r="A176" s="61" t="str">
+        <x:v>BCSE102L</x:v>
+      </x:c>
+      <x:c r="B176" s="62" t="str">
+        <x:v>Structured and Object-Oriented Programming</x:v>
+      </x:c>
+      <x:c r="C176" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D176" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E176" s="62" t="str">
+        <x:v>PRP330</x:v>
+      </x:c>
+      <x:c r="F176" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G176" s="63" t="str">
+        <x:v>SUKANTA GHOSH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="15" hidden="0" customHeight="1">
+      <x:c r="A177" s="61" t="str">
+        <x:v>BCSE102L</x:v>
+      </x:c>
+      <x:c r="B177" s="62" t="str">
+        <x:v>Structured and Object-Oriented Programming</x:v>
+      </x:c>
+      <x:c r="C177" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D177" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E177" s="62" t="str">
+        <x:v>PRP330</x:v>
+      </x:c>
+      <x:c r="F177" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G177" s="63" t="str">
+        <x:v>SUKANTA GHOSH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="15" hidden="0" customHeight="1">
+      <x:c r="A178" s="61" t="str">
+        <x:v>BCSE102P</x:v>
+      </x:c>
+      <x:c r="B178" s="62" t="str">
+        <x:v>Structured and Object-Oriented Programming Lab</x:v>
+      </x:c>
+      <x:c r="C178" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D178" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E178" s="62" t="str">
+        <x:v>PRP347</x:v>
+      </x:c>
+      <x:c r="F178" s="62" t="str">
+        <x:v>L39+L40+L55+L56</x:v>
+      </x:c>
+      <x:c r="G178" s="63" t="str">
+        <x:v>SUKANTA GHOSH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="15" hidden="0" customHeight="1">
+      <x:c r="A179" s="61" t="str">
+        <x:v>BCSE102P</x:v>
+      </x:c>
+      <x:c r="B179" s="62" t="str">
+        <x:v>Structured and Object-Oriented Programming Lab</x:v>
+      </x:c>
+      <x:c r="C179" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D179" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E179" s="62" t="str">
+        <x:v>PRP138</x:v>
+      </x:c>
+      <x:c r="F179" s="62" t="str">
+        <x:v>L13+L14+L27+L28</x:v>
+      </x:c>
+      <x:c r="G179" s="63" t="str">
+        <x:v>SUKANTA GHOSH</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14bb34c55d274206"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9479282cab684baf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/util/report_vellore.xlsx
+++ b/util/report_vellore.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FFCS Data" sheetId="1" r:id="Re4b7e09a8c044a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FFCS Data" sheetId="1" r:id="R12e28a09f306488b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -485,7 +485,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FFCSDataTable" displayName="FFCSDataTable" ref="A1:G179" headerRowCount="1" totalsRowCount="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FFCSDataTable" displayName="FFCSDataTable" ref="A1:G259" headerRowCount="1" totalsRowCount="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="CODE"/>
     <x:tableColumn id="2" name="TITLE"/>
@@ -4017,140 +4017,140 @@
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
       <x:c r="A147" s="61" t="str">
-        <x:v>BITE404E</x:v>
+        <x:v>BITE301L</x:v>
       </x:c>
       <x:c r="B147" s="62" t="str">
-        <x:v>Object Oriented Analysis and Design</x:v>
+        <x:v>Computer Architecture and Organization</x:v>
       </x:c>
       <x:c r="C147" s="62" t="str">
-        <x:v>ETH</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D147" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E147" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP426</x:v>
       </x:c>
       <x:c r="F147" s="62" t="str">
-        <x:v>G1</x:v>
+        <x:v>A1+TA1</x:v>
       </x:c>
       <x:c r="G147" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>KARPAGAM S</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
       <x:c r="A148" s="61" t="str">
-        <x:v>BITE404E</x:v>
+        <x:v>BCSE102L</x:v>
       </x:c>
       <x:c r="B148" s="62" t="str">
-        <x:v>Object Oriented Analysis and Design</x:v>
+        <x:v>Structured and Object-Oriented Programming</x:v>
       </x:c>
       <x:c r="C148" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D148" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E148" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP330</x:v>
       </x:c>
       <x:c r="F148" s="62" t="str">
-        <x:v>L55+L56</x:v>
+        <x:v>D1</x:v>
       </x:c>
       <x:c r="G148" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUKANTA GHOSH</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="61" t="str">
-        <x:v>BITE404E</x:v>
+        <x:v>BCSE102L</x:v>
       </x:c>
       <x:c r="B149" s="62" t="str">
-        <x:v>Object Oriented Analysis and Design</x:v>
+        <x:v>Structured and Object-Oriented Programming</x:v>
       </x:c>
       <x:c r="C149" s="62" t="str">
-        <x:v>ETH</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D149" s="107" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E149" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP330</x:v>
       </x:c>
       <x:c r="F149" s="62" t="str">
-        <x:v>G2</x:v>
+        <x:v>D2</x:v>
       </x:c>
       <x:c r="G149" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUKANTA GHOSH</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="61" t="str">
-        <x:v>BITE404E</x:v>
+        <x:v>BCSE102P</x:v>
       </x:c>
       <x:c r="B150" s="62" t="str">
-        <x:v>Object Oriented Analysis and Design</x:v>
+        <x:v>Structured and Object-Oriented Programming Lab</x:v>
       </x:c>
       <x:c r="C150" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>LO</x:v>
       </x:c>
       <x:c r="D150" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E150" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP347</x:v>
       </x:c>
       <x:c r="F150" s="62" t="str">
-        <x:v>L3+L4</x:v>
+        <x:v>L39+L40+L55+L56</x:v>
       </x:c>
       <x:c r="G150" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUKANTA GHOSH</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
       <x:c r="A151" s="61" t="str">
-        <x:v>BITE404E</x:v>
+        <x:v>BCSE102P</x:v>
       </x:c>
       <x:c r="B151" s="62" t="str">
-        <x:v>Object Oriented Analysis and Design</x:v>
+        <x:v>Structured and Object-Oriented Programming Lab</x:v>
       </x:c>
       <x:c r="C151" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>LO</x:v>
       </x:c>
       <x:c r="D151" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E151" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP138</x:v>
       </x:c>
       <x:c r="F151" s="62" t="str">
-        <x:v>L45+L46</x:v>
+        <x:v>L13+L14+L27+L28</x:v>
       </x:c>
       <x:c r="G151" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUKANTA GHOSH</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
       <x:c r="A152" s="61" t="str">
-        <x:v>BITE404E</x:v>
+        <x:v>BITE311L</x:v>
       </x:c>
       <x:c r="B152" s="62" t="str">
-        <x:v>Object Oriented Analysis and Design</x:v>
+        <x:v>Human Computer Interaction</x:v>
       </x:c>
       <x:c r="C152" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D152" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E152" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT823</x:v>
       </x:c>
       <x:c r="F152" s="62" t="str">
-        <x:v>L25+L26</x:v>
+        <x:v>E2+TE2</x:v>
       </x:c>
       <x:c r="G152" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>AASEEGHA M D</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -4167,13 +4167,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E153" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT803</x:v>
       </x:c>
       <x:c r="F153" s="62" t="str">
-        <x:v>E1+TE1</x:v>
+        <x:v>E2+TE2</x:v>
       </x:c>
       <x:c r="G153" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>BHUVANESWARI M S</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -4190,36 +4190,36 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E154" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJTG24</x:v>
       </x:c>
       <x:c r="F154" s="62" t="str">
-        <x:v>E2+TE2</x:v>
+        <x:v>E1+TE1</x:v>
       </x:c>
       <x:c r="G154" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>JENILA VINCENT M</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="61" t="str">
-        <x:v>BITE312E</x:v>
+        <x:v>BITE311L</x:v>
       </x:c>
       <x:c r="B155" s="62" t="str">
-        <x:v>Data Mining</x:v>
+        <x:v>Human Computer Interaction</x:v>
       </x:c>
       <x:c r="C155" s="62" t="str">
-        <x:v>ETH</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D155" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E155" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT824</x:v>
       </x:c>
       <x:c r="F155" s="62" t="str">
-        <x:v>G1</x:v>
+        <x:v>E1+TE1</x:v>
       </x:c>
       <x:c r="G155" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>DEEPA P</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -4230,19 +4230,19 @@
         <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C156" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D156" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E156" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT824</x:v>
       </x:c>
       <x:c r="F156" s="62" t="str">
-        <x:v>L49+L50</x:v>
+        <x:v>G2</x:v>
       </x:c>
       <x:c r="G156" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SENTHILKUMAR N C</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -4253,19 +4253,19 @@
         <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C157" s="62" t="str">
-        <x:v>ETH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D157" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E157" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJTG20</x:v>
       </x:c>
       <x:c r="F157" s="62" t="str">
-        <x:v>G2</x:v>
+        <x:v>L49+L50</x:v>
       </x:c>
       <x:c r="G157" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRABHANANTHA KUMAR M</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -4276,19 +4276,19 @@
         <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C158" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D158" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E158" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT105</x:v>
       </x:c>
       <x:c r="F158" s="62" t="str">
-        <x:v>L11+L12</x:v>
+        <x:v>G1</x:v>
       </x:c>
       <x:c r="G158" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>YOGA RAJA C A</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -4305,13 +4305,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E159" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJTG20</x:v>
       </x:c>
       <x:c r="F159" s="62" t="str">
-        <x:v>L51+L52</x:v>
+        <x:v>L1+L2</x:v>
       </x:c>
       <x:c r="G159" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>JAI KUMARAN</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -4322,280 +4322,280 @@
         <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C160" s="62" t="str">
-        <x:v>ELA</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D160" s="107" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E160" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP230</x:v>
       </x:c>
       <x:c r="F160" s="62" t="str">
-        <x:v>L1+L2</x:v>
+        <x:v>G2</x:v>
       </x:c>
       <x:c r="G160" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>JAI KUMARAN</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
       <x:c r="A161" s="61" t="str">
-        <x:v>BITE401L</x:v>
+        <x:v>BITE312E</x:v>
       </x:c>
       <x:c r="B161" s="62" t="str">
-        <x:v>Network and Information Security</x:v>
+        <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C161" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D161" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E161" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT712</x:v>
       </x:c>
       <x:c r="F161" s="62" t="str">
-        <x:v>A1+TA1</x:v>
+        <x:v>G1</x:v>
       </x:c>
       <x:c r="G161" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRABHANANTHA KUMAR M</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
       <x:c r="A162" s="61" t="str">
-        <x:v>BITE401L</x:v>
+        <x:v>BITE312E</x:v>
       </x:c>
       <x:c r="B162" s="62" t="str">
-        <x:v>Network and Information Security</x:v>
+        <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C162" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D162" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E162" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJTG20</x:v>
       </x:c>
       <x:c r="F162" s="62" t="str">
-        <x:v>A2+TA2</x:v>
+        <x:v>L51+L52</x:v>
       </x:c>
       <x:c r="G162" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>YOGA RAJA C A</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
       <x:c r="A163" s="61" t="str">
-        <x:v>BITE402L</x:v>
+        <x:v>BITE312E</x:v>
       </x:c>
       <x:c r="B163" s="62" t="str">
-        <x:v>Distributed Computing</x:v>
+        <x:v>Data Mining</x:v>
       </x:c>
       <x:c r="C163" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D163" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E163" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJTG20</x:v>
       </x:c>
       <x:c r="F163" s="62" t="str">
-        <x:v>B1+TB1</x:v>
+        <x:v>L11+L12</x:v>
       </x:c>
       <x:c r="G163" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SENTHILKUMAR N C</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
       <x:c r="A164" s="61" t="str">
-        <x:v>BITE402L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B164" s="62" t="str">
-        <x:v>Distributed Computing</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C164" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D164" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E164" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT219</x:v>
       </x:c>
       <x:c r="F164" s="62" t="str">
-        <x:v>B2+TB2</x:v>
+        <x:v>L45+L46</x:v>
       </x:c>
       <x:c r="G164" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SRIVATHSAVA M</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
       <x:c r="A165" s="61" t="str">
-        <x:v>BITE405L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B165" s="62" t="str">
-        <x:v>Soft Computing</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C165" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D165" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E165" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJTG20</x:v>
       </x:c>
       <x:c r="F165" s="62" t="str">
-        <x:v>C1+TC1</x:v>
+        <x:v>L3+L4</x:v>
       </x:c>
       <x:c r="G165" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SRIVATHSAVA M</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="61" t="str">
-        <x:v>BITE405L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B166" s="62" t="str">
-        <x:v>Soft Computing</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C166" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D166" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E166" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT219</x:v>
       </x:c>
       <x:c r="F166" s="62" t="str">
-        <x:v>C2+TC2</x:v>
+        <x:v>L25+L26</x:v>
       </x:c>
       <x:c r="G166" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUJANA M</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="61" t="str">
-        <x:v>BITE409L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B167" s="62" t="str">
-        <x:v>Mobile Application Development</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C167" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D167" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E167" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT709</x:v>
       </x:c>
       <x:c r="F167" s="62" t="str">
-        <x:v>C1+TC1</x:v>
+        <x:v>G2</x:v>
       </x:c>
       <x:c r="G167" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SRIVATHSAVA M</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="61" t="str">
-        <x:v>BITE409L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B168" s="62" t="str">
-        <x:v>Mobile Application Development</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C168" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D168" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E168" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT711</x:v>
       </x:c>
       <x:c r="F168" s="62" t="str">
-        <x:v>C2+TC2</x:v>
+        <x:v>G1</x:v>
       </x:c>
       <x:c r="G168" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUGANYA A</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="61" t="str">
-        <x:v>BITE410L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B169" s="62" t="str">
-        <x:v>Machine Learning</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C169" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D169" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E169" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>PRP426</x:v>
       </x:c>
       <x:c r="F169" s="62" t="str">
-        <x:v>E1+TE1</x:v>
+        <x:v>G1</x:v>
       </x:c>
       <x:c r="G169" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SRIVATHSAVA M</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
       <x:c r="A170" s="61" t="str">
-        <x:v>BITE410L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B170" s="62" t="str">
-        <x:v>Machine Learning</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C170" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D170" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E170" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT711</x:v>
       </x:c>
       <x:c r="F170" s="62" t="str">
-        <x:v>E2+TE2</x:v>
+        <x:v>G2</x:v>
       </x:c>
       <x:c r="G170" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUJANA M</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
       <x:c r="A171" s="61" t="str">
-        <x:v>BITE411L</x:v>
+        <x:v>BITE404E</x:v>
       </x:c>
       <x:c r="B171" s="62" t="str">
-        <x:v>Big Data Analytics</x:v>
+        <x:v>Object Oriented Analysis and Design</x:v>
       </x:c>
       <x:c r="C171" s="62" t="str">
-        <x:v>TH</x:v>
+        <x:v>ELA</x:v>
       </x:c>
       <x:c r="D171" s="107" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E171" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT122</x:v>
       </x:c>
       <x:c r="F171" s="62" t="str">
-        <x:v>D1+TD1</x:v>
+        <x:v>L55+L56</x:v>
       </x:c>
       <x:c r="G171" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SUGANYA A</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="61" t="str">
-        <x:v>BITE411L</x:v>
+        <x:v>BITE405L</x:v>
       </x:c>
       <x:c r="B172" s="62" t="str">
-        <x:v>Big Data Analytics</x:v>
+        <x:v>Soft Computing</x:v>
       </x:c>
       <x:c r="C172" s="62" t="str">
         <x:v>TH</x:v>
@@ -4604,21 +4604,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E172" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT211</x:v>
       </x:c>
       <x:c r="F172" s="62" t="str">
-        <x:v>D2+TD2</x:v>
+        <x:v>C2+TC2</x:v>
       </x:c>
       <x:c r="G172" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>BRIJENDRA SINGH</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
       <x:c r="A173" s="61" t="str">
-        <x:v>BSTS302P</x:v>
+        <x:v>BITE405L</x:v>
       </x:c>
       <x:c r="B173" s="62" t="str">
-        <x:v>Advanced Competitive Coding - II</x:v>
+        <x:v>Soft Computing</x:v>
       </x:c>
       <x:c r="C173" s="62" t="str">
         <x:v>TH</x:v>
@@ -4627,21 +4627,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E173" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT825</x:v>
       </x:c>
       <x:c r="F173" s="62" t="str">
-        <x:v>F1</x:v>
+        <x:v>C2+TC2</x:v>
       </x:c>
       <x:c r="G173" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>NEELU KHARE</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
       <x:c r="A174" s="61" t="str">
-        <x:v>BSTS302P</x:v>
+        <x:v>BITE405L</x:v>
       </x:c>
       <x:c r="B174" s="62" t="str">
-        <x:v>Advanced Competitive Coding - II</x:v>
+        <x:v>Soft Computing</x:v>
       </x:c>
       <x:c r="C174" s="62" t="str">
         <x:v>TH</x:v>
@@ -4650,21 +4650,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E174" s="62" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>SJT807</x:v>
       </x:c>
       <x:c r="F174" s="62" t="str">
-        <x:v>F2</x:v>
+        <x:v>C1+TC1</x:v>
       </x:c>
       <x:c r="G174" s="63" t="str">
-        <x:v>Not announced</x:v>
+        <x:v>CHIRANJI LAL CHOWDHARY</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
       <x:c r="A175" s="61" t="str">
-        <x:v>BITE301L</x:v>
+        <x:v>BITE405L</x:v>
       </x:c>
       <x:c r="B175" s="62" t="str">
-        <x:v>Computer Architecture and Organization</x:v>
+        <x:v>Soft Computing</x:v>
       </x:c>
       <x:c r="C175" s="62" t="str">
         <x:v>TH</x:v>
@@ -4673,111 +4673,1951 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E175" s="62" t="str">
-        <x:v>PRP426</x:v>
+        <x:v>SJT825</x:v>
       </x:c>
       <x:c r="F175" s="62" t="str">
-        <x:v>A1+TA1</x:v>
+        <x:v>C1+TC1</x:v>
       </x:c>
       <x:c r="G175" s="63" t="str">
-        <x:v>KARPAGAM S</x:v>
+        <x:v>NEELU KHARE</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
       <x:c r="A176" s="61" t="str">
-        <x:v>BCSE102L</x:v>
+        <x:v>BITE409L</x:v>
       </x:c>
       <x:c r="B176" s="62" t="str">
-        <x:v>Structured and Object-Oriented Programming</x:v>
+        <x:v>Mobile Application Development</x:v>
       </x:c>
       <x:c r="C176" s="62" t="str">
         <x:v>TH</x:v>
       </x:c>
       <x:c r="D176" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E176" s="62" t="str">
-        <x:v>PRP330</x:v>
+        <x:v>SJT823</x:v>
       </x:c>
       <x:c r="F176" s="62" t="str">
-        <x:v>D1</x:v>
+        <x:v>C1+TC1</x:v>
       </x:c>
       <x:c r="G176" s="63" t="str">
-        <x:v>SUKANTA GHOSH</x:v>
+        <x:v>SENTHIL KUMARAN U</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
       <x:c r="A177" s="61" t="str">
-        <x:v>BCSE102L</x:v>
+        <x:v>BITE409L</x:v>
       </x:c>
       <x:c r="B177" s="62" t="str">
-        <x:v>Structured and Object-Oriented Programming</x:v>
+        <x:v>Mobile Application Development</x:v>
       </x:c>
       <x:c r="C177" s="62" t="str">
         <x:v>TH</x:v>
       </x:c>
       <x:c r="D177" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E177" s="62" t="str">
-        <x:v>PRP330</x:v>
+        <x:v>SJT824</x:v>
       </x:c>
       <x:c r="F177" s="62" t="str">
-        <x:v>D2</x:v>
+        <x:v>C2+TC2</x:v>
       </x:c>
       <x:c r="G177" s="63" t="str">
-        <x:v>SUKANTA GHOSH</x:v>
+        <x:v>SHUNMUGA PERUMAL P</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
       <x:c r="A178" s="61" t="str">
-        <x:v>BCSE102P</x:v>
+        <x:v>BITE409L</x:v>
       </x:c>
       <x:c r="B178" s="62" t="str">
-        <x:v>Structured and Object-Oriented Programming Lab</x:v>
+        <x:v>Mobile Application Development</x:v>
       </x:c>
       <x:c r="C178" s="62" t="str">
-        <x:v>LO</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D178" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E178" s="62" t="str">
-        <x:v>PRP347</x:v>
+        <x:v>SJT824</x:v>
       </x:c>
       <x:c r="F178" s="62" t="str">
-        <x:v>L39+L40+L55+L56</x:v>
+        <x:v>C1+TC1</x:v>
       </x:c>
       <x:c r="G178" s="63" t="str">
-        <x:v>SUKANTA GHOSH</x:v>
+        <x:v>SHUNMUGA PERUMAL P</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
       <x:c r="A179" s="61" t="str">
-        <x:v>BCSE102P</x:v>
+        <x:v>BITE409L</x:v>
       </x:c>
       <x:c r="B179" s="62" t="str">
-        <x:v>Structured and Object-Oriented Programming Lab</x:v>
+        <x:v>Mobile Application Development</x:v>
       </x:c>
       <x:c r="C179" s="62" t="str">
-        <x:v>LO</x:v>
+        <x:v>TH</x:v>
       </x:c>
       <x:c r="D179" s="107" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E179" s="62" t="str">
-        <x:v>PRP138</x:v>
+        <x:v>SJT807</x:v>
       </x:c>
       <x:c r="F179" s="62" t="str">
-        <x:v>L13+L14+L27+L28</x:v>
+        <x:v>C2+TC2</x:v>
       </x:c>
       <x:c r="G179" s="63" t="str">
-        <x:v>SUKANTA GHOSH</x:v>
+        <x:v>JEEVITHA P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="15" hidden="0" customHeight="1">
+      <x:c r="A180" s="61" t="str">
+        <x:v>BITE410L</x:v>
+      </x:c>
+      <x:c r="B180" s="62" t="str">
+        <x:v>Machine Learning</x:v>
+      </x:c>
+      <x:c r="C180" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D180" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E180" s="62" t="str">
+        <x:v>SJT103</x:v>
+      </x:c>
+      <x:c r="F180" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G180" s="63" t="str">
+        <x:v>DHIVYA E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="15" hidden="0" customHeight="1">
+      <x:c r="A181" s="61" t="str">
+        <x:v>BITE410L</x:v>
+      </x:c>
+      <x:c r="B181" s="62" t="str">
+        <x:v>Machine Learning</x:v>
+      </x:c>
+      <x:c r="C181" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D181" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E181" s="62" t="str">
+        <x:v>SJT109</x:v>
+      </x:c>
+      <x:c r="F181" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G181" s="63" t="str">
+        <x:v>NIVEDITA S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="15" hidden="0" customHeight="1">
+      <x:c r="A182" s="61" t="str">
+        <x:v>BITE410L</x:v>
+      </x:c>
+      <x:c r="B182" s="62" t="str">
+        <x:v>Machine Learning</x:v>
+      </x:c>
+      <x:c r="C182" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D182" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E182" s="62" t="str">
+        <x:v>SJT115</x:v>
+      </x:c>
+      <x:c r="F182" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G182" s="63" t="str">
+        <x:v>KISHORERAJA P C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="15" hidden="0" customHeight="1">
+      <x:c r="A183" s="61" t="str">
+        <x:v>BITE410L</x:v>
+      </x:c>
+      <x:c r="B183" s="62" t="str">
+        <x:v>Machine Learning</x:v>
+      </x:c>
+      <x:c r="C183" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D183" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E183" s="62" t="str">
+        <x:v>SJT125</x:v>
+      </x:c>
+      <x:c r="F183" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G183" s="63" t="str">
+        <x:v>JAGANNATHAN J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="15" hidden="0" customHeight="1">
+      <x:c r="A184" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B184" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C184" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D184" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E184" s="62" t="str">
+        <x:v>SJT104</x:v>
+      </x:c>
+      <x:c r="F184" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G184" s="63" t="str">
+        <x:v>ASIS KUMAR TRIPATHY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="15" hidden="0" customHeight="1">
+      <x:c r="A185" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B185" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C185" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D185" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E185" s="62" t="str">
+        <x:v>SJT825</x:v>
+      </x:c>
+      <x:c r="F185" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G185" s="63" t="str">
+        <x:v>MEENATCHI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="15" hidden="0" customHeight="1">
+      <x:c r="A186" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B186" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C186" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D186" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E186" s="62" t="str">
+        <x:v>SJT125</x:v>
+      </x:c>
+      <x:c r="F186" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G186" s="63" t="str">
+        <x:v>THANGA MARIAPPAN L</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="15" hidden="0" customHeight="1">
+      <x:c r="A187" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B187" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C187" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D187" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E187" s="62" t="str">
+        <x:v>SJTG24</x:v>
+      </x:c>
+      <x:c r="F187" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G187" s="63" t="str">
+        <x:v>THANGA MARIAPPAN L</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="15" hidden="0" customHeight="1">
+      <x:c r="A188" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B188" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C188" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D188" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E188" s="62" t="str">
+        <x:v>SJT124</x:v>
+      </x:c>
+      <x:c r="F188" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G188" s="63" t="str">
+        <x:v>MEENATCHI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="15" hidden="0" customHeight="1">
+      <x:c r="A189" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B189" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C189" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D189" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E189" s="62" t="str">
+        <x:v>SJT103</x:v>
+      </x:c>
+      <x:c r="F189" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G189" s="63" t="str">
+        <x:v>SRINIVAS KOPPU</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="15" hidden="0" customHeight="1">
+      <x:c r="A190" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B190" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C190" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D190" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E190" s="62" t="str">
+        <x:v>SJT104</x:v>
+      </x:c>
+      <x:c r="F190" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G190" s="63" t="str">
+        <x:v>SRINIVAS KOPPU</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="15" hidden="0" customHeight="1">
+      <x:c r="A191" s="61" t="str">
+        <x:v>BITE401L</x:v>
+      </x:c>
+      <x:c r="B191" s="62" t="str">
+        <x:v>Network and Information Security</x:v>
+      </x:c>
+      <x:c r="C191" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D191" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E191" s="62" t="str">
+        <x:v>SJT101</x:v>
+      </x:c>
+      <x:c r="F191" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G191" s="63" t="str">
+        <x:v>ASIS KUMAR TRIPATHY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" ht="15" hidden="0" customHeight="1">
+      <x:c r="A192" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B192" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C192" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D192" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E192" s="62" t="str">
+        <x:v>SJT709</x:v>
+      </x:c>
+      <x:c r="F192" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G192" s="63" t="str">
+        <x:v>VANI M P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" ht="15" hidden="0" customHeight="1">
+      <x:c r="A193" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B193" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C193" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D193" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E193" s="62" t="str">
+        <x:v>SJT707</x:v>
+      </x:c>
+      <x:c r="F193" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G193" s="63" t="str">
+        <x:v>VANI M P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="15" hidden="0" customHeight="1">
+      <x:c r="A194" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B194" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C194" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D194" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E194" s="62" t="str">
+        <x:v>SJT807</x:v>
+      </x:c>
+      <x:c r="F194" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G194" s="63" t="str">
+        <x:v>RATHI R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="15" hidden="0" customHeight="1">
+      <x:c r="A195" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B195" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C195" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D195" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E195" s="62" t="str">
+        <x:v>SJT802</x:v>
+      </x:c>
+      <x:c r="F195" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G195" s="63" t="str">
+        <x:v>VENKETESH P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="15" hidden="0" customHeight="1">
+      <x:c r="A196" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B196" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C196" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D196" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E196" s="62" t="str">
+        <x:v>SJT803</x:v>
+      </x:c>
+      <x:c r="F196" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G196" s="63" t="str">
+        <x:v>VENKETESH P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="15" hidden="0" customHeight="1">
+      <x:c r="A197" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B197" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C197" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D197" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E197" s="62" t="str">
+        <x:v>SJT715</x:v>
+      </x:c>
+      <x:c r="F197" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G197" s="63" t="str">
+        <x:v>SENTHILKUMAR T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="15" hidden="0" customHeight="1">
+      <x:c r="A198" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B198" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C198" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D198" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E198" s="62" t="str">
+        <x:v>SJT712</x:v>
+      </x:c>
+      <x:c r="F198" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G198" s="63" t="str">
+        <x:v>MEENATCHI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="15" hidden="0" customHeight="1">
+      <x:c r="A199" s="61" t="str">
+        <x:v>BITE402L</x:v>
+      </x:c>
+      <x:c r="B199" s="62" t="str">
+        <x:v>Distributed Computing</x:v>
+      </x:c>
+      <x:c r="C199" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D199" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E199" s="62" t="str">
+        <x:v>SJT626</x:v>
+      </x:c>
+      <x:c r="F199" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G199" s="63" t="str">
+        <x:v>BHUVANA S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="15" hidden="0" customHeight="1">
+      <x:c r="A200" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B200" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C200" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D200" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E200" s="62" t="str">
+        <x:v>SJTG14</x:v>
+      </x:c>
+      <x:c r="F200" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G200" s="63" t="str">
+        <x:v>RATHI R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="15" hidden="0" customHeight="1">
+      <x:c r="A201" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B201" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C201" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D201" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E201" s="62" t="str">
+        <x:v>SJT824</x:v>
+      </x:c>
+      <x:c r="F201" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G201" s="63" t="str">
+        <x:v>HARSHITA PATEL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="15" hidden="0" customHeight="1">
+      <x:c r="A202" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B202" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C202" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D202" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E202" s="62" t="str">
+        <x:v>SJTG16</x:v>
+      </x:c>
+      <x:c r="F202" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G202" s="63" t="str">
+        <x:v>RAJESH P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="15" hidden="0" customHeight="1">
+      <x:c r="A203" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B203" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C203" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D203" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E203" s="62" t="str">
+        <x:v>SJTG24</x:v>
+      </x:c>
+      <x:c r="F203" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G203" s="63" t="str">
+        <x:v>PRAVEEN KUMAR REDDY M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="15" hidden="0" customHeight="1">
+      <x:c r="A204" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B204" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C204" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D204" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E204" s="62" t="str">
+        <x:v>SJT825</x:v>
+      </x:c>
+      <x:c r="F204" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G204" s="63" t="str">
+        <x:v>RATHI R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="15" hidden="0" customHeight="1">
+      <x:c r="A205" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B205" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C205" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D205" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E205" s="62" t="str">
+        <x:v>SJT825</x:v>
+      </x:c>
+      <x:c r="F205" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G205" s="63" t="str">
+        <x:v>CHANDRA MOULISWARAN S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="15" hidden="0" customHeight="1">
+      <x:c r="A206" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B206" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C206" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D206" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E206" s="62" t="str">
+        <x:v>SJT824</x:v>
+      </x:c>
+      <x:c r="F206" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G206" s="63" t="str">
+        <x:v>CHANDRA MOULISWARAN S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="15" hidden="0" customHeight="1">
+      <x:c r="A207" s="61" t="str">
+        <x:v>BITE411L</x:v>
+      </x:c>
+      <x:c r="B207" s="62" t="str">
+        <x:v>Big Data Analytics</x:v>
+      </x:c>
+      <x:c r="C207" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D207" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E207" s="62" t="str">
+        <x:v>SJT823</x:v>
+      </x:c>
+      <x:c r="F207" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G207" s="63" t="str">
+        <x:v>PADMAKUMARI P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="15" hidden="0" customHeight="1">
+      <x:c r="A208" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B208" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C208" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D208" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E208" s="62" t="str">
+        <x:v>SMV218</x:v>
+      </x:c>
+      <x:c r="F208" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G208" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="15" hidden="0" customHeight="1">
+      <x:c r="A209" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B209" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C209" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D209" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E209" s="62" t="str">
+        <x:v>SMV218</x:v>
+      </x:c>
+      <x:c r="F209" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G209" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="15" hidden="0" customHeight="1">
+      <x:c r="A210" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B210" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C210" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D210" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E210" s="62" t="str">
+        <x:v>SMV219</x:v>
+      </x:c>
+      <x:c r="F210" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G210" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="15" hidden="0" customHeight="1">
+      <x:c r="A211" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B211" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C211" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D211" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E211" s="62" t="str">
+        <x:v>SMV102</x:v>
+      </x:c>
+      <x:c r="F211" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G211" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="15" hidden="0" customHeight="1">
+      <x:c r="A212" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B212" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C212" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D212" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E212" s="62" t="str">
+        <x:v>CDMM405</x:v>
+      </x:c>
+      <x:c r="F212" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G212" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="15" hidden="0" customHeight="1">
+      <x:c r="A213" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B213" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C213" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D213" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E213" s="62" t="str">
+        <x:v>TT630</x:v>
+      </x:c>
+      <x:c r="F213" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G213" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="15" hidden="0" customHeight="1">
+      <x:c r="A214" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B214" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C214" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D214" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E214" s="62" t="str">
+        <x:v>SJT201</x:v>
+      </x:c>
+      <x:c r="F214" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G214" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="15" hidden="0" customHeight="1">
+      <x:c r="A215" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B215" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C215" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D215" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E215" s="62" t="str">
+        <x:v>SJT202</x:v>
+      </x:c>
+      <x:c r="F215" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G215" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="15" hidden="0" customHeight="1">
+      <x:c r="A216" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B216" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C216" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D216" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E216" s="62" t="str">
+        <x:v>SJT204</x:v>
+      </x:c>
+      <x:c r="F216" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G216" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="15" hidden="0" customHeight="1">
+      <x:c r="A217" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B217" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C217" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D217" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E217" s="62" t="str">
+        <x:v>SJT208</x:v>
+      </x:c>
+      <x:c r="F217" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G217" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="15" hidden="0" customHeight="1">
+      <x:c r="A218" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B218" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C218" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D218" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E218" s="62" t="str">
+        <x:v>SJT211</x:v>
+      </x:c>
+      <x:c r="F218" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G218" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="15" hidden="0" customHeight="1">
+      <x:c r="A219" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B219" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C219" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D219" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E219" s="62" t="str">
+        <x:v>SJT211</x:v>
+      </x:c>
+      <x:c r="F219" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G219" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="15" hidden="0" customHeight="1">
+      <x:c r="A220" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B220" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C220" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D220" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E220" s="62" t="str">
+        <x:v>GDN121</x:v>
+      </x:c>
+      <x:c r="F220" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G220" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="15" hidden="0" customHeight="1">
+      <x:c r="A221" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B221" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C221" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D221" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E221" s="62" t="str">
+        <x:v>GDN122</x:v>
+      </x:c>
+      <x:c r="F221" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G221" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="15" hidden="0" customHeight="1">
+      <x:c r="A222" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B222" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C222" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D222" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E222" s="62" t="str">
+        <x:v>GDN107</x:v>
+      </x:c>
+      <x:c r="F222" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G222" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="15" hidden="0" customHeight="1">
+      <x:c r="A223" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B223" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C223" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D223" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E223" s="62" t="str">
+        <x:v>GDN107</x:v>
+      </x:c>
+      <x:c r="F223" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G223" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="15" hidden="0" customHeight="1">
+      <x:c r="A224" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B224" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C224" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D224" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E224" s="62" t="str">
+        <x:v>GDN121</x:v>
+      </x:c>
+      <x:c r="F224" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G224" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="15" hidden="0" customHeight="1">
+      <x:c r="A225" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B225" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C225" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D225" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E225" s="62" t="str">
+        <x:v>SMV219</x:v>
+      </x:c>
+      <x:c r="F225" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G225" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="15" hidden="0" customHeight="1">
+      <x:c r="A226" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B226" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C226" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D226" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E226" s="62" t="str">
+        <x:v>TT404</x:v>
+      </x:c>
+      <x:c r="F226" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G226" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="15" hidden="0" customHeight="1">
+      <x:c r="A227" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B227" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C227" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D227" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E227" s="62" t="str">
+        <x:v>SJT204</x:v>
+      </x:c>
+      <x:c r="F227" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G227" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" ht="15" hidden="0" customHeight="1">
+      <x:c r="A228" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B228" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C228" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D228" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E228" s="62" t="str">
+        <x:v>SJT205</x:v>
+      </x:c>
+      <x:c r="F228" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G228" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" ht="15" hidden="0" customHeight="1">
+      <x:c r="A229" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B229" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C229" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D229" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E229" s="62" t="str">
+        <x:v>SJT205</x:v>
+      </x:c>
+      <x:c r="F229" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G229" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" ht="15" hidden="0" customHeight="1">
+      <x:c r="A230" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B230" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C230" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D230" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E230" s="62" t="str">
+        <x:v>SJT208</x:v>
+      </x:c>
+      <x:c r="F230" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G230" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" ht="15" hidden="0" customHeight="1">
+      <x:c r="A231" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B231" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C231" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D231" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E231" s="62" t="str">
+        <x:v>GDN120</x:v>
+      </x:c>
+      <x:c r="F231" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G231" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" ht="15" hidden="0" customHeight="1">
+      <x:c r="A232" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B232" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C232" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D232" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E232" s="62" t="str">
+        <x:v>GDN122</x:v>
+      </x:c>
+      <x:c r="F232" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G232" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" ht="15" hidden="0" customHeight="1">
+      <x:c r="A233" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B233" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C233" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D233" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E233" s="62" t="str">
+        <x:v>SMV102</x:v>
+      </x:c>
+      <x:c r="F233" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G233" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" ht="15" hidden="0" customHeight="1">
+      <x:c r="A234" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B234" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C234" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D234" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E234" s="62" t="str">
+        <x:v>TT630</x:v>
+      </x:c>
+      <x:c r="F234" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G234" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" ht="15" hidden="0" customHeight="1">
+      <x:c r="A235" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B235" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C235" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D235" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E235" s="62" t="str">
+        <x:v>CDMM405</x:v>
+      </x:c>
+      <x:c r="F235" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G235" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="15" hidden="0" customHeight="1">
+      <x:c r="A236" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B236" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C236" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D236" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E236" s="62" t="str">
+        <x:v>GDN106</x:v>
+      </x:c>
+      <x:c r="F236" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G236" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" ht="15" hidden="0" customHeight="1">
+      <x:c r="A237" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B237" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C237" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D237" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E237" s="62" t="str">
+        <x:v>GDN120</x:v>
+      </x:c>
+      <x:c r="F237" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G237" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" ht="15" hidden="0" customHeight="1">
+      <x:c r="A238" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B238" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C238" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D238" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E238" s="62" t="str">
+        <x:v>GDN123</x:v>
+      </x:c>
+      <x:c r="F238" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G238" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" ht="15" hidden="0" customHeight="1">
+      <x:c r="A239" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B239" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C239" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D239" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E239" s="62" t="str">
+        <x:v>TT524</x:v>
+      </x:c>
+      <x:c r="F239" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G239" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" ht="15" hidden="0" customHeight="1">
+      <x:c r="A240" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B240" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C240" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D240" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E240" s="62" t="str">
+        <x:v>TT531</x:v>
+      </x:c>
+      <x:c r="F240" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G240" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" ht="15" hidden="0" customHeight="1">
+      <x:c r="A241" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B241" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C241" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D241" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E241" s="62" t="str">
+        <x:v>TT531</x:v>
+      </x:c>
+      <x:c r="F241" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G241" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" ht="15" hidden="0" customHeight="1">
+      <x:c r="A242" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B242" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C242" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D242" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E242" s="62" t="str">
+        <x:v>TT404</x:v>
+      </x:c>
+      <x:c r="F242" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G242" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" ht="15" hidden="0" customHeight="1">
+      <x:c r="A243" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B243" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C243" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D243" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E243" s="62" t="str">
+        <x:v>SJT201</x:v>
+      </x:c>
+      <x:c r="F243" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G243" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" ht="15" hidden="0" customHeight="1">
+      <x:c r="A244" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B244" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C244" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D244" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E244" s="62" t="str">
+        <x:v>SJT202</x:v>
+      </x:c>
+      <x:c r="F244" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G244" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" ht="15" hidden="0" customHeight="1">
+      <x:c r="A245" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B245" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C245" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D245" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E245" s="62" t="str">
+        <x:v>TT523</x:v>
+      </x:c>
+      <x:c r="F245" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G245" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" ht="15" hidden="0" customHeight="1">
+      <x:c r="A246" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B246" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C246" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D246" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E246" s="62" t="str">
+        <x:v>TT523</x:v>
+      </x:c>
+      <x:c r="F246" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G246" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" ht="15" hidden="0" customHeight="1">
+      <x:c r="A247" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B247" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C247" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D247" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E247" s="62" t="str">
+        <x:v>GDN106</x:v>
+      </x:c>
+      <x:c r="F247" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G247" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" ht="15" hidden="0" customHeight="1">
+      <x:c r="A248" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B248" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C248" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D248" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E248" s="62" t="str">
+        <x:v>GDN123</x:v>
+      </x:c>
+      <x:c r="F248" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G248" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" ht="15" hidden="0" customHeight="1">
+      <x:c r="A249" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B249" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C249" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D249" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E249" s="62" t="str">
+        <x:v>TT530</x:v>
+      </x:c>
+      <x:c r="F249" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G249" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" ht="15" hidden="0" customHeight="1">
+      <x:c r="A250" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B250" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C250" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D250" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E250" s="62" t="str">
+        <x:v>TT530A</x:v>
+      </x:c>
+      <x:c r="F250" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G250" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" ht="15" hidden="0" customHeight="1">
+      <x:c r="A251" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B251" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C251" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D251" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E251" s="62" t="str">
+        <x:v>TT531A</x:v>
+      </x:c>
+      <x:c r="F251" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G251" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" ht="15" hidden="0" customHeight="1">
+      <x:c r="A252" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B252" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C252" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D252" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E252" s="62" t="str">
+        <x:v>TT531A</x:v>
+      </x:c>
+      <x:c r="F252" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G252" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" ht="15" hidden="0" customHeight="1">
+      <x:c r="A253" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B253" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C253" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D253" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E253" s="62" t="str">
+        <x:v>TT504</x:v>
+      </x:c>
+      <x:c r="F253" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G253" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" ht="15" hidden="0" customHeight="1">
+      <x:c r="A254" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B254" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C254" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D254" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E254" s="62" t="str">
+        <x:v>TT504</x:v>
+      </x:c>
+      <x:c r="F254" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G254" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" ht="15" hidden="0" customHeight="1">
+      <x:c r="A255" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B255" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C255" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D255" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E255" s="62" t="str">
+        <x:v>TT524</x:v>
+      </x:c>
+      <x:c r="F255" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G255" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" ht="15" hidden="0" customHeight="1">
+      <x:c r="A256" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B256" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C256" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D256" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E256" s="62" t="str">
+        <x:v>TT530A</x:v>
+      </x:c>
+      <x:c r="F256" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G256" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" ht="15" hidden="0" customHeight="1">
+      <x:c r="A257" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B257" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C257" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D257" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E257" s="62" t="str">
+        <x:v>TT434</x:v>
+      </x:c>
+      <x:c r="F257" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G257" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" ht="15" hidden="0" customHeight="1">
+      <x:c r="A258" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B258" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C258" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D258" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E258" s="62" t="str">
+        <x:v>TT530</x:v>
+      </x:c>
+      <x:c r="F258" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G258" s="63" t="str">
+        <x:v>ETHNUS (APT)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" ht="15" hidden="0" customHeight="1">
+      <x:c r="A259" s="61" t="str">
+        <x:v>BSTS302P</x:v>
+      </x:c>
+      <x:c r="B259" s="62" t="str">
+        <x:v>Advanced Competitive Coding - II</x:v>
+      </x:c>
+      <x:c r="C259" s="62" t="str">
+        <x:v>SS</x:v>
+      </x:c>
+      <x:c r="D259" s="107" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="E259" s="62" t="str">
+        <x:v>TT434</x:v>
+      </x:c>
+      <x:c r="F259" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G259" s="63" t="str">
+        <x:v>FACE (APT)</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9479282cab684baf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0c54b304b574bec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/util/report_vellore.xlsx
+++ b/util/report_vellore.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FFCS Data" sheetId="1" r:id="R12e28a09f306488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FFCS Data" sheetId="1" r:id="R86f748aaab334003"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -485,7 +485,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FFCSDataTable" displayName="FFCSDataTable" ref="A1:G259" headerRowCount="1" totalsRowCount="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FFCSDataTable" displayName="FFCSDataTable" ref="A1:G513" headerRowCount="1" totalsRowCount="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="CODE"/>
     <x:tableColumn id="2" name="TITLE"/>
@@ -6614,10 +6614,5852 @@
         <x:v>FACE (APT)</x:v>
       </x:c>
     </x:row>
+    <x:row r="260" ht="15" hidden="0" customHeight="1">
+      <x:c r="A260" s="61" t="str">
+        <x:v>BARB101L</x:v>
+      </x:c>
+      <x:c r="B260" s="62" t="str">
+        <x:v>Arabic</x:v>
+      </x:c>
+      <x:c r="C260" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D260" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E260" s="62" t="str">
+        <x:v>PRP230</x:v>
+      </x:c>
+      <x:c r="F260" s="62" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="G260" s="63" t="str">
+        <x:v>MOHD SAQIB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" ht="15" hidden="0" customHeight="1">
+      <x:c r="A261" s="61" t="str">
+        <x:v>BARB101L</x:v>
+      </x:c>
+      <x:c r="B261" s="62" t="str">
+        <x:v>Arabic</x:v>
+      </x:c>
+      <x:c r="C261" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D261" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E261" s="62" t="str">
+        <x:v>PRP230</x:v>
+      </x:c>
+      <x:c r="F261" s="62" t="str">
+        <x:v>C1</x:v>
+      </x:c>
+      <x:c r="G261" s="63" t="str">
+        <x:v>MOHD SAQIB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" ht="15" hidden="0" customHeight="1">
+      <x:c r="A262" s="61" t="str">
+        <x:v>BCHI101L</x:v>
+      </x:c>
+      <x:c r="B262" s="62" t="str">
+        <x:v>Chinese I</x:v>
+      </x:c>
+      <x:c r="C262" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D262" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E262" s="62" t="str">
+        <x:v>PRP104</x:v>
+      </x:c>
+      <x:c r="F262" s="62" t="str">
+        <x:v>G1</x:v>
+      </x:c>
+      <x:c r="G262" s="63" t="str">
+        <x:v>KHANA BAIDYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" ht="15" hidden="0" customHeight="1">
+      <x:c r="A263" s="61" t="str">
+        <x:v>BCHI101L</x:v>
+      </x:c>
+      <x:c r="B263" s="62" t="str">
+        <x:v>Chinese I</x:v>
+      </x:c>
+      <x:c r="C263" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D263" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E263" s="62" t="str">
+        <x:v>SJT105</x:v>
+      </x:c>
+      <x:c r="F263" s="62" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="G263" s="63" t="str">
+        <x:v>KHANA BAIDYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" ht="15" hidden="0" customHeight="1">
+      <x:c r="A264" s="61" t="str">
+        <x:v>BCHY101L</x:v>
+      </x:c>
+      <x:c r="B264" s="62" t="str">
+        <x:v>Engineering Chemistry</x:v>
+      </x:c>
+      <x:c r="C264" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D264" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E264" s="62" t="str">
+        <x:v>PRP630</x:v>
+      </x:c>
+      <x:c r="F264" s="62" t="str">
+        <x:v>G2+TG2</x:v>
+      </x:c>
+      <x:c r="G264" s="63" t="str">
+        <x:v>SATHISH KUMAR P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" ht="15" hidden="0" customHeight="1">
+      <x:c r="A265" s="61" t="str">
+        <x:v>BCHY101L</x:v>
+      </x:c>
+      <x:c r="B265" s="62" t="str">
+        <x:v>Engineering Chemistry</x:v>
+      </x:c>
+      <x:c r="C265" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D265" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E265" s="62" t="str">
+        <x:v>PRP434</x:v>
+      </x:c>
+      <x:c r="F265" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G265" s="63" t="str">
+        <x:v>ATANU CHAKRABORTY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" ht="15" hidden="0" customHeight="1">
+      <x:c r="A266" s="61" t="str">
+        <x:v>BCHY101P</x:v>
+      </x:c>
+      <x:c r="B266" s="62" t="str">
+        <x:v>Engineering Chemistry Lab</x:v>
+      </x:c>
+      <x:c r="C266" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D266" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E266" s="62" t="str">
+        <x:v>PRP408A</x:v>
+      </x:c>
+      <x:c r="F266" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G266" s="63" t="str">
+        <x:v>ASHINA CHANDRAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" ht="15" hidden="0" customHeight="1">
+      <x:c r="A267" s="61" t="str">
+        <x:v>BCHY101P</x:v>
+      </x:c>
+      <x:c r="B267" s="62" t="str">
+        <x:v>Engineering Chemistry Lab</x:v>
+      </x:c>
+      <x:c r="C267" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D267" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E267" s="62" t="str">
+        <x:v>PRP408A</x:v>
+      </x:c>
+      <x:c r="F267" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G267" s="63" t="str">
+        <x:v>ASHINA CHANDRAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" ht="15" hidden="0" customHeight="1">
+      <x:c r="A268" s="61" t="str">
+        <x:v>BCHY101P</x:v>
+      </x:c>
+      <x:c r="B268" s="62" t="str">
+        <x:v>Engineering Chemistry Lab</x:v>
+      </x:c>
+      <x:c r="C268" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D268" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E268" s="62" t="str">
+        <x:v>PRP408A</x:v>
+      </x:c>
+      <x:c r="F268" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G268" s="63" t="str">
+        <x:v>SATHISH KUMAR P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" ht="15" hidden="0" customHeight="1">
+      <x:c r="A269" s="61" t="str">
+        <x:v>BCHY101P</x:v>
+      </x:c>
+      <x:c r="B269" s="62" t="str">
+        <x:v>Engineering Chemistry Lab</x:v>
+      </x:c>
+      <x:c r="C269" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D269" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E269" s="62" t="str">
+        <x:v>PRP408A</x:v>
+      </x:c>
+      <x:c r="F269" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G269" s="63" t="str">
+        <x:v>ATANU CHAKRABORTY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" ht="15" hidden="0" customHeight="1">
+      <x:c r="A270" s="61" t="str">
+        <x:v>BCLE212L</x:v>
+      </x:c>
+      <x:c r="B270" s="62" t="str">
+        <x:v>Natural Disaster Mitigation and Management</x:v>
+      </x:c>
+      <x:c r="C270" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D270" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E270" s="62" t="str">
+        <x:v>CDMM104</x:v>
+      </x:c>
+      <x:c r="F270" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G270" s="63" t="str">
+        <x:v>MEENA T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" ht="15" hidden="0" customHeight="1">
+      <x:c r="A271" s="61" t="str">
+        <x:v>BCLE214L</x:v>
+      </x:c>
+      <x:c r="B271" s="62" t="str">
+        <x:v>Global Warming</x:v>
+      </x:c>
+      <x:c r="C271" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D271" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E271" s="62" t="str">
+        <x:v>CDMM105</x:v>
+      </x:c>
+      <x:c r="F271" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G271" s="63" t="str">
+        <x:v>KAVITHA M.S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" ht="15" hidden="0" customHeight="1">
+      <x:c r="A272" s="61" t="str">
+        <x:v>BCLE214L</x:v>
+      </x:c>
+      <x:c r="B272" s="62" t="str">
+        <x:v>Global Warming</x:v>
+      </x:c>
+      <x:c r="C272" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D272" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E272" s="62" t="str">
+        <x:v>CDMM403</x:v>
+      </x:c>
+      <x:c r="F272" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G272" s="63" t="str">
+        <x:v>VIGNESH RAJKUMAR L</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" ht="15" hidden="0" customHeight="1">
+      <x:c r="A273" s="61" t="str">
+        <x:v>BCLE216L</x:v>
+      </x:c>
+      <x:c r="B273" s="62" t="str">
+        <x:v>Water Resource Management</x:v>
+      </x:c>
+      <x:c r="C273" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D273" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E273" s="62" t="str">
+        <x:v>CDMM104</x:v>
+      </x:c>
+      <x:c r="F273" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G273" s="63" t="str">
+        <x:v>MAHENTHIRAN S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" ht="15" hidden="0" customHeight="1">
+      <x:c r="A274" s="61" t="str">
+        <x:v>BCLE216L</x:v>
+      </x:c>
+      <x:c r="B274" s="62" t="str">
+        <x:v>Water Resource Management</x:v>
+      </x:c>
+      <x:c r="C274" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D274" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E274" s="62" t="str">
+        <x:v>CDMM105</x:v>
+      </x:c>
+      <x:c r="F274" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G274" s="63" t="str">
+        <x:v>PARIMALA RENGANAYAKI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" ht="15" hidden="0" customHeight="1">
+      <x:c r="A275" s="61" t="str">
+        <x:v>BCLE216L</x:v>
+      </x:c>
+      <x:c r="B275" s="62" t="str">
+        <x:v>Water Resource Management</x:v>
+      </x:c>
+      <x:c r="C275" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D275" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E275" s="62" t="str">
+        <x:v>CDMM104</x:v>
+      </x:c>
+      <x:c r="F275" s="62" t="str">
+        <x:v>D1+TD1</x:v>
+      </x:c>
+      <x:c r="G275" s="63" t="str">
+        <x:v>VIGNESH RAJKUMAR L</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" ht="15" hidden="0" customHeight="1">
+      <x:c r="A276" s="61" t="str">
+        <x:v>BCSE101E</x:v>
+      </x:c>
+      <x:c r="B276" s="62" t="str">
+        <x:v>Computer Programming: Python</x:v>
+      </x:c>
+      <x:c r="C276" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D276" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E276" s="62" t="str">
+        <x:v>SJT301</x:v>
+      </x:c>
+      <x:c r="F276" s="62" t="str">
+        <x:v>TCC1</x:v>
+      </x:c>
+      <x:c r="G276" s="63" t="str">
+        <x:v>KAVITHA G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" ht="15" hidden="0" customHeight="1">
+      <x:c r="A277" s="61" t="str">
+        <x:v>BCSE101E</x:v>
+      </x:c>
+      <x:c r="B277" s="62" t="str">
+        <x:v>Computer Programming: Python</x:v>
+      </x:c>
+      <x:c r="C277" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D277" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E277" s="62" t="str">
+        <x:v>SJT318</x:v>
+      </x:c>
+      <x:c r="F277" s="62" t="str">
+        <x:v>L31+L32+L41+L42</x:v>
+      </x:c>
+      <x:c r="G277" s="63" t="str">
+        <x:v>KAVITHA G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" ht="15" hidden="0" customHeight="1">
+      <x:c r="A278" s="61" t="str">
+        <x:v>BCSE103E</x:v>
+      </x:c>
+      <x:c r="B278" s="62" t="str">
+        <x:v>Computer Programming: Java</x:v>
+      </x:c>
+      <x:c r="C278" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D278" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E278" s="62" t="str">
+        <x:v>PRP125</x:v>
+      </x:c>
+      <x:c r="F278" s="62" t="str">
+        <x:v>TAA1</x:v>
+      </x:c>
+      <x:c r="G278" s="63" t="str">
+        <x:v>MOHAMED YOUSUFF A R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" ht="15" hidden="0" customHeight="1">
+      <x:c r="A279" s="61" t="str">
+        <x:v>BCSE103E</x:v>
+      </x:c>
+      <x:c r="B279" s="62" t="str">
+        <x:v>Computer Programming: Java</x:v>
+      </x:c>
+      <x:c r="C279" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D279" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E279" s="62" t="str">
+        <x:v>SJT304</x:v>
+      </x:c>
+      <x:c r="F279" s="62" t="str">
+        <x:v>TAA2</x:v>
+      </x:c>
+      <x:c r="G279" s="63" t="str">
+        <x:v>UMA PRIYA D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" ht="15" hidden="0" customHeight="1">
+      <x:c r="A280" s="61" t="str">
+        <x:v>BCSE103E</x:v>
+      </x:c>
+      <x:c r="B280" s="62" t="str">
+        <x:v>Computer Programming: Java</x:v>
+      </x:c>
+      <x:c r="C280" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D280" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E280" s="62" t="str">
+        <x:v>PRP234</x:v>
+      </x:c>
+      <x:c r="F280" s="62" t="str">
+        <x:v>L35+L36+L51+L52</x:v>
+      </x:c>
+      <x:c r="G280" s="63" t="str">
+        <x:v>MOHAMED YOUSUFF A R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" ht="15" hidden="0" customHeight="1">
+      <x:c r="A281" s="61" t="str">
+        <x:v>BCSE103E</x:v>
+      </x:c>
+      <x:c r="B281" s="62" t="str">
+        <x:v>Computer Programming: Java</x:v>
+      </x:c>
+      <x:c r="C281" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D281" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E281" s="62" t="str">
+        <x:v>SJT416</x:v>
+      </x:c>
+      <x:c r="F281" s="62" t="str">
+        <x:v>L5+L6+L19+L20</x:v>
+      </x:c>
+      <x:c r="G281" s="63" t="str">
+        <x:v>UMA PRIYA D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" ht="15" hidden="0" customHeight="1">
+      <x:c r="A282" s="61" t="str">
+        <x:v>BEEE102L</x:v>
+      </x:c>
+      <x:c r="B282" s="62" t="str">
+        <x:v>Basic Electrical and Electronics Engineering</x:v>
+      </x:c>
+      <x:c r="C282" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D282" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E282" s="62" t="str">
+        <x:v>TT404</x:v>
+      </x:c>
+      <x:c r="F282" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G282" s="63" t="str">
+        <x:v>BELWIN EDWARD J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" ht="15" hidden="0" customHeight="1">
+      <x:c r="A283" s="61" t="str">
+        <x:v>BEEE102L</x:v>
+      </x:c>
+      <x:c r="B283" s="62" t="str">
+        <x:v>Basic Electrical and Electronics Engineering</x:v>
+      </x:c>
+      <x:c r="C283" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D283" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E283" s="62" t="str">
+        <x:v>TT404</x:v>
+      </x:c>
+      <x:c r="F283" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G283" s="63" t="str">
+        <x:v>MEIKANDASIVAM S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" ht="15" hidden="0" customHeight="1">
+      <x:c r="A284" s="61" t="str">
+        <x:v>BEEE102P</x:v>
+      </x:c>
+      <x:c r="B284" s="62" t="str">
+        <x:v>Basic Electrical and Electronics Engineering Lab</x:v>
+      </x:c>
+      <x:c r="C284" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D284" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E284" s="62" t="str">
+        <x:v>TT344</x:v>
+      </x:c>
+      <x:c r="F284" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G284" s="63" t="str">
+        <x:v>BELWIN EDWARD J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" ht="15" hidden="0" customHeight="1">
+      <x:c r="A285" s="61" t="str">
+        <x:v>BEEE102P</x:v>
+      </x:c>
+      <x:c r="B285" s="62" t="str">
+        <x:v>Basic Electrical and Electronics Engineering Lab</x:v>
+      </x:c>
+      <x:c r="C285" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D285" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E285" s="62" t="str">
+        <x:v>TT344</x:v>
+      </x:c>
+      <x:c r="F285" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G285" s="63" t="str">
+        <x:v>BELWIN EDWARD J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" ht="15" hidden="0" customHeight="1">
+      <x:c r="A286" s="61" t="str">
+        <x:v>BEEE102P</x:v>
+      </x:c>
+      <x:c r="B286" s="62" t="str">
+        <x:v>Basic Electrical and Electronics Engineering Lab</x:v>
+      </x:c>
+      <x:c r="C286" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D286" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E286" s="62" t="str">
+        <x:v>TT344</x:v>
+      </x:c>
+      <x:c r="F286" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G286" s="63" t="str">
+        <x:v>MEIKANDASIVAM S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" ht="15" hidden="0" customHeight="1">
+      <x:c r="A287" s="61" t="str">
+        <x:v>BEEE102P</x:v>
+      </x:c>
+      <x:c r="B287" s="62" t="str">
+        <x:v>Basic Electrical and Electronics Engineering Lab</x:v>
+      </x:c>
+      <x:c r="C287" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D287" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E287" s="62" t="str">
+        <x:v>TT344</x:v>
+      </x:c>
+      <x:c r="F287" s="62" t="str">
+        <x:v>L5+L6</x:v>
+      </x:c>
+      <x:c r="G287" s="63" t="str">
+        <x:v>MEIKANDASIVAM S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" ht="15" hidden="0" customHeight="1">
+      <x:c r="A288" s="61" t="str">
+        <x:v>BENG101L</x:v>
+      </x:c>
+      <x:c r="B288" s="62" t="str">
+        <x:v>Technical English Communication</x:v>
+      </x:c>
+      <x:c r="C288" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D288" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E288" s="62" t="str">
+        <x:v>SJT409</x:v>
+      </x:c>
+      <x:c r="F288" s="62" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="G288" s="63" t="str">
+        <x:v>DENISH RAJA DURAI K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" ht="15" hidden="0" customHeight="1">
+      <x:c r="A289" s="61" t="str">
+        <x:v>BENG101P</x:v>
+      </x:c>
+      <x:c r="B289" s="62" t="str">
+        <x:v>Technical English Communication Lab</x:v>
+      </x:c>
+      <x:c r="C289" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D289" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E289" s="62" t="str">
+        <x:v>PRP249</x:v>
+      </x:c>
+      <x:c r="F289" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G289" s="63" t="str">
+        <x:v>DENISH RAJA DURAI K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" ht="15" hidden="0" customHeight="1">
+      <x:c r="A290" s="61" t="str">
+        <x:v>BENG102P</x:v>
+      </x:c>
+      <x:c r="B290" s="62" t="str">
+        <x:v>Technical Report Writing</x:v>
+      </x:c>
+      <x:c r="C290" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D290" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E290" s="62" t="str">
+        <x:v>TT432</x:v>
+      </x:c>
+      <x:c r="F290" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G290" s="63" t="str">
+        <x:v>ANBURAJ G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" ht="15" hidden="0" customHeight="1">
+      <x:c r="A291" s="61" t="str">
+        <x:v>BESP101L</x:v>
+      </x:c>
+      <x:c r="B291" s="62" t="str">
+        <x:v>Spanish I</x:v>
+      </x:c>
+      <x:c r="C291" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D291" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E291" s="62" t="str">
+        <x:v>SJT409</x:v>
+      </x:c>
+      <x:c r="F291" s="62" t="str">
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="G291" s="63" t="str">
+        <x:v>SHILPI GUPTA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" ht="15" hidden="0" customHeight="1">
+      <x:c r="A292" s="61" t="str">
+        <x:v>BESP101L</x:v>
+      </x:c>
+      <x:c r="B292" s="62" t="str">
+        <x:v>Spanish I</x:v>
+      </x:c>
+      <x:c r="C292" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D292" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E292" s="62" t="str">
+        <x:v>SJT222</x:v>
+      </x:c>
+      <x:c r="F292" s="62" t="str">
+        <x:v>F2</x:v>
+      </x:c>
+      <x:c r="G292" s="63" t="str">
+        <x:v>NUPUR MANASI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" ht="15" hidden="0" customHeight="1">
+      <x:c r="A293" s="61" t="str">
+        <x:v>BESP101L</x:v>
+      </x:c>
+      <x:c r="B293" s="62" t="str">
+        <x:v>Spanish I</x:v>
+      </x:c>
+      <x:c r="C293" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D293" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E293" s="62" t="str">
+        <x:v>SJT201</x:v>
+      </x:c>
+      <x:c r="F293" s="62" t="str">
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="G293" s="63" t="str">
+        <x:v>BAISHALI CHOUDHURI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" ht="15" hidden="0" customHeight="1">
+      <x:c r="A294" s="61" t="str">
+        <x:v>BESP101L</x:v>
+      </x:c>
+      <x:c r="B294" s="62" t="str">
+        <x:v>Spanish I</x:v>
+      </x:c>
+      <x:c r="C294" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D294" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E294" s="62" t="str">
+        <x:v>SJT126</x:v>
+      </x:c>
+      <x:c r="F294" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G294" s="63" t="str">
+        <x:v>NUPUR MANASI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" ht="15" hidden="0" customHeight="1">
+      <x:c r="A295" s="61" t="str">
+        <x:v>BESP101L</x:v>
+      </x:c>
+      <x:c r="B295" s="62" t="str">
+        <x:v>Spanish I</x:v>
+      </x:c>
+      <x:c r="C295" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D295" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E295" s="62" t="str">
+        <x:v>SMV123</x:v>
+      </x:c>
+      <x:c r="F295" s="62" t="str">
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="G295" s="63" t="str">
+        <x:v>SABYASACHI MISHRA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" ht="15" hidden="0" customHeight="1">
+      <x:c r="A296" s="61" t="str">
+        <x:v>BFRE101L</x:v>
+      </x:c>
+      <x:c r="B296" s="62" t="str">
+        <x:v>French I</x:v>
+      </x:c>
+      <x:c r="C296" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D296" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E296" s="62" t="str">
+        <x:v>PRP223</x:v>
+      </x:c>
+      <x:c r="F296" s="62" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="G296" s="63" t="str">
+        <x:v>SHANTANU SHANDILYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" ht="15" hidden="0" customHeight="1">
+      <x:c r="A297" s="61" t="str">
+        <x:v>BFRE101L</x:v>
+      </x:c>
+      <x:c r="B297" s="62" t="str">
+        <x:v>French I</x:v>
+      </x:c>
+      <x:c r="C297" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D297" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E297" s="62" t="str">
+        <x:v>SMV130</x:v>
+      </x:c>
+      <x:c r="F297" s="62" t="str">
+        <x:v>E2</x:v>
+      </x:c>
+      <x:c r="G297" s="63" t="str">
+        <x:v>MALATHY O</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" ht="15" hidden="0" customHeight="1">
+      <x:c r="A298" s="61" t="str">
+        <x:v>BFRE101L</x:v>
+      </x:c>
+      <x:c r="B298" s="62" t="str">
+        <x:v>French I</x:v>
+      </x:c>
+      <x:c r="C298" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D298" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E298" s="62" t="str">
+        <x:v>PRP429</x:v>
+      </x:c>
+      <x:c r="F298" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G298" s="63" t="str">
+        <x:v>SHANTANU SHANDILYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" ht="15" hidden="0" customHeight="1">
+      <x:c r="A299" s="61" t="str">
+        <x:v>BFRE101L</x:v>
+      </x:c>
+      <x:c r="B299" s="62" t="str">
+        <x:v>French I</x:v>
+      </x:c>
+      <x:c r="C299" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D299" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E299" s="62" t="str">
+        <x:v>TT104</x:v>
+      </x:c>
+      <x:c r="F299" s="62" t="str">
+        <x:v>E1</x:v>
+      </x:c>
+      <x:c r="G299" s="63" t="str">
+        <x:v>COUMARAN G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" ht="15" hidden="0" customHeight="1">
+      <x:c r="A300" s="61" t="str">
+        <x:v>BFRE101L</x:v>
+      </x:c>
+      <x:c r="B300" s="62" t="str">
+        <x:v>French I</x:v>
+      </x:c>
+      <x:c r="C300" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D300" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E300" s="62" t="str">
+        <x:v>SMV101</x:v>
+      </x:c>
+      <x:c r="F300" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G300" s="63" t="str">
+        <x:v>COUMARAN G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" ht="15" hidden="0" customHeight="1">
+      <x:c r="A301" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B301" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C301" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D301" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E301" s="62" t="str">
+        <x:v>SJT709</x:v>
+      </x:c>
+      <x:c r="F301" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G301" s="63" t="str">
+        <x:v>AMIT KUMAR SAINI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" ht="15" hidden="0" customHeight="1">
+      <x:c r="A302" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B302" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C302" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D302" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E302" s="62" t="str">
+        <x:v>SJT415</x:v>
+      </x:c>
+      <x:c r="F302" s="62" t="str">
+        <x:v>G2</x:v>
+      </x:c>
+      <x:c r="G302" s="63" t="str">
+        <x:v>DHANANJAY KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" ht="15" hidden="0" customHeight="1">
+      <x:c r="A303" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B303" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C303" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D303" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E303" s="62" t="str">
+        <x:v>SJT315</x:v>
+      </x:c>
+      <x:c r="F303" s="62" t="str">
+        <x:v>A2</x:v>
+      </x:c>
+      <x:c r="G303" s="63" t="str">
+        <x:v>ABHIJIT KR DARBEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" ht="15" hidden="0" customHeight="1">
+      <x:c r="A304" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B304" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C304" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D304" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E304" s="62" t="str">
+        <x:v>SJT303</x:v>
+      </x:c>
+      <x:c r="F304" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G304" s="63" t="str">
+        <x:v>DHANANJAY KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" ht="15" hidden="0" customHeight="1">
+      <x:c r="A305" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B305" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C305" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D305" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E305" s="62" t="str">
+        <x:v>SJT127</x:v>
+      </x:c>
+      <x:c r="F305" s="62" t="str">
+        <x:v>A2</x:v>
+      </x:c>
+      <x:c r="G305" s="63" t="str">
+        <x:v>ARATI KUMARI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" ht="15" hidden="0" customHeight="1">
+      <x:c r="A306" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B306" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C306" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D306" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E306" s="62" t="str">
+        <x:v>SJT202</x:v>
+      </x:c>
+      <x:c r="F306" s="62" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="G306" s="63" t="str">
+        <x:v>ARATI KUMARI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" ht="15" hidden="0" customHeight="1">
+      <x:c r="A307" s="61" t="str">
+        <x:v>BGER101L</x:v>
+      </x:c>
+      <x:c r="B307" s="62" t="str">
+        <x:v>German I</x:v>
+      </x:c>
+      <x:c r="C307" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D307" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E307" s="62" t="str">
+        <x:v>SJT302</x:v>
+      </x:c>
+      <x:c r="F307" s="62" t="str">
+        <x:v>F1</x:v>
+      </x:c>
+      <x:c r="G307" s="63" t="str">
+        <x:v>ABHIJIT KR DARBEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" ht="15" hidden="0" customHeight="1">
+      <x:c r="A308" s="61" t="str">
+        <x:v>BHUM108L</x:v>
+      </x:c>
+      <x:c r="B308" s="62" t="str">
+        <x:v>Urban Community Development</x:v>
+      </x:c>
+      <x:c r="C308" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D308" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E308" s="62" t="str">
+        <x:v>SJT409</x:v>
+      </x:c>
+      <x:c r="F308" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G308" s="63" t="str">
+        <x:v>BALAMURUGAN J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" ht="15" hidden="0" customHeight="1">
+      <x:c r="A309" s="61" t="str">
+        <x:v>BJAP101L</x:v>
+      </x:c>
+      <x:c r="B309" s="62" t="str">
+        <x:v>Japanese I</x:v>
+      </x:c>
+      <x:c r="C309" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D309" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E309" s="62" t="str">
+        <x:v>SJT405</x:v>
+      </x:c>
+      <x:c r="F309" s="62" t="str">
+        <x:v>A2</x:v>
+      </x:c>
+      <x:c r="G309" s="63" t="str">
+        <x:v>KHANJAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" ht="15" hidden="0" customHeight="1">
+      <x:c r="A310" s="61" t="str">
+        <x:v>BJAP101L</x:v>
+      </x:c>
+      <x:c r="B310" s="62" t="str">
+        <x:v>Japanese I</x:v>
+      </x:c>
+      <x:c r="C310" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D310" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E310" s="62" t="str">
+        <x:v>SMV214</x:v>
+      </x:c>
+      <x:c r="F310" s="62" t="str">
+        <x:v>C2</x:v>
+      </x:c>
+      <x:c r="G310" s="63" t="str">
+        <x:v>HIYA MUKHERJEE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" ht="15" hidden="0" customHeight="1">
+      <x:c r="A311" s="61" t="str">
+        <x:v>BMAT101L</x:v>
+      </x:c>
+      <x:c r="B311" s="62" t="str">
+        <x:v>Calculus</x:v>
+      </x:c>
+      <x:c r="C311" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D311" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E311" s="62" t="str">
+        <x:v>SJT223</x:v>
+      </x:c>
+      <x:c r="F311" s="62" t="str">
+        <x:v>D2+TD2</x:v>
+      </x:c>
+      <x:c r="G311" s="63" t="str">
+        <x:v>GORINTLA SUCHARITHA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" ht="15" hidden="0" customHeight="1">
+      <x:c r="A312" s="61" t="str">
+        <x:v>BMAT101P</x:v>
+      </x:c>
+      <x:c r="B312" s="62" t="str">
+        <x:v>Calculus Lab</x:v>
+      </x:c>
+      <x:c r="C312" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D312" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E312" s="62" t="str">
+        <x:v>PRP447</x:v>
+      </x:c>
+      <x:c r="F312" s="62" t="str">
+        <x:v>L3+L4</x:v>
+      </x:c>
+      <x:c r="G312" s="63" t="str">
+        <x:v>GORINTLA SUCHARITHA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A313" s="61" t="str">
+        <x:v>BMAT102L</x:v>
+      </x:c>
+      <x:c r="B313" s="62" t="str">
+        <x:v>Differential Equations and Transforms</x:v>
+      </x:c>
+      <x:c r="C313" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D313" s="107" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E313" s="62" t="str">
+        <x:v>SJT407</x:v>
+      </x:c>
+      <x:c r="F313" s="62" t="str">
+        <x:v>B2+TB2+TBB2</x:v>
+      </x:c>
+      <x:c r="G313" s="63" t="str">
+        <x:v>AKELLA VENKATA SURYANARAYANA MURTY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" ht="15" hidden="0" customHeight="1">
+      <x:c r="A314" s="61" t="str">
+        <x:v>BMAT102L</x:v>
+      </x:c>
+      <x:c r="B314" s="62" t="str">
+        <x:v>Differential Equations and Transforms</x:v>
+      </x:c>
+      <x:c r="C314" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D314" s="107" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E314" s="62" t="str">
+        <x:v>SJT617</x:v>
+      </x:c>
+      <x:c r="F314" s="62" t="str">
+        <x:v>C1+TC1+TCC1</x:v>
+      </x:c>
+      <x:c r="G314" s="63" t="str">
+        <x:v>INDHIRA K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" ht="15" hidden="0" customHeight="1">
+      <x:c r="A315" s="61" t="str">
+        <x:v>BMAT201L</x:v>
+      </x:c>
+      <x:c r="B315" s="62" t="str">
+        <x:v>Complex Variables and Linear Algebra</x:v>
+      </x:c>
+      <x:c r="C315" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D315" s="107" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E315" s="62" t="str">
+        <x:v>SJT415</x:v>
+      </x:c>
+      <x:c r="F315" s="62" t="str">
+        <x:v>C1+TC1+TCC1</x:v>
+      </x:c>
+      <x:c r="G315" s="63" t="str">
+        <x:v>MURUGUSUNDARAMOORTHY G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" ht="15" hidden="0" customHeight="1">
+      <x:c r="A316" s="61" t="str">
+        <x:v>BMAT201L</x:v>
+      </x:c>
+      <x:c r="B316" s="62" t="str">
+        <x:v>Complex Variables and Linear Algebra</x:v>
+      </x:c>
+      <x:c r="C316" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D316" s="107" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E316" s="62" t="str">
+        <x:v>SJT405</x:v>
+      </x:c>
+      <x:c r="F316" s="62" t="str">
+        <x:v>C2+TC2+TCC2</x:v>
+      </x:c>
+      <x:c r="G316" s="63" t="str">
+        <x:v>VIJAYA K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" ht="15" hidden="0" customHeight="1">
+      <x:c r="A317" s="61" t="str">
+        <x:v>BMAT202L</x:v>
+      </x:c>
+      <x:c r="B317" s="62" t="str">
+        <x:v>Probability and Statistics</x:v>
+      </x:c>
+      <x:c r="C317" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D317" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E317" s="62" t="str">
+        <x:v>SMV123</x:v>
+      </x:c>
+      <x:c r="F317" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G317" s="63" t="str">
+        <x:v>DINESH KUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" ht="15" hidden="0" customHeight="1">
+      <x:c r="A318" s="61" t="str">
+        <x:v>BMAT202L</x:v>
+      </x:c>
+      <x:c r="B318" s="62" t="str">
+        <x:v>Probability and Statistics</x:v>
+      </x:c>
+      <x:c r="C318" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D318" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E318" s="62" t="str">
+        <x:v>TT523</x:v>
+      </x:c>
+      <x:c r="F318" s="62" t="str">
+        <x:v>G2+TG2</x:v>
+      </x:c>
+      <x:c r="G318" s="63" t="str">
+        <x:v>INDHIRA K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" ht="15" hidden="0" customHeight="1">
+      <x:c r="A319" s="61" t="str">
+        <x:v>BMAT202P</x:v>
+      </x:c>
+      <x:c r="B319" s="62" t="str">
+        <x:v>Probability and Statistics Lab</x:v>
+      </x:c>
+      <x:c r="C319" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D319" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E319" s="62" t="str">
+        <x:v>PRP119</x:v>
+      </x:c>
+      <x:c r="F319" s="62" t="str">
+        <x:v>L55+L56</x:v>
+      </x:c>
+      <x:c r="G319" s="63" t="str">
+        <x:v>DINESH KUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" ht="15" hidden="0" customHeight="1">
+      <x:c r="A320" s="61" t="str">
+        <x:v>BMGT101L</x:v>
+      </x:c>
+      <x:c r="B320" s="62" t="str">
+        <x:v>Principles of Management</x:v>
+      </x:c>
+      <x:c r="C320" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D320" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E320" s="62" t="str">
+        <x:v>MB229</x:v>
+      </x:c>
+      <x:c r="F320" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G320" s="63" t="str">
+        <x:v>NATARAJ G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" ht="15" hidden="0" customHeight="1">
+      <x:c r="A321" s="61" t="str">
+        <x:v>BPHY101L</x:v>
+      </x:c>
+      <x:c r="B321" s="62" t="str">
+        <x:v>Engineering Physics</x:v>
+      </x:c>
+      <x:c r="C321" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D321" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E321" s="62" t="str">
+        <x:v>TT413</x:v>
+      </x:c>
+      <x:c r="F321" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G321" s="63" t="str">
+        <x:v>RAJAN BABU D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" ht="15" hidden="0" customHeight="1">
+      <x:c r="A322" s="61" t="str">
+        <x:v>BPHY101P</x:v>
+      </x:c>
+      <x:c r="B322" s="62" t="str">
+        <x:v>Engineering Physics Lab</x:v>
+      </x:c>
+      <x:c r="C322" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D322" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E322" s="62" t="str">
+        <x:v>TT420</x:v>
+      </x:c>
+      <x:c r="F322" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G322" s="63" t="str">
+        <x:v>RAJAN BABU D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" ht="15" hidden="0" customHeight="1">
+      <x:c r="A323" s="61" t="str">
+        <x:v>BECE203L</x:v>
+      </x:c>
+      <x:c r="B323" s="62" t="str">
+        <x:v>Circuit Theory</x:v>
+      </x:c>
+      <x:c r="C323" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D323" s="107" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E323" s="62" t="str">
+        <x:v>TT631</x:v>
+      </x:c>
+      <x:c r="F323" s="62" t="str">
+        <x:v>A2+TA2+TAA2</x:v>
+      </x:c>
+      <x:c r="G323" s="63" t="str">
+        <x:v>TANGUDU RAMJI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" ht="15" hidden="0" customHeight="1">
+      <x:c r="A324" s="61" t="str">
+        <x:v>BECE102L</x:v>
+      </x:c>
+      <x:c r="B324" s="62" t="str">
+        <x:v>Digital Systems Design</x:v>
+      </x:c>
+      <x:c r="C324" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D324" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E324" s="62" t="str">
+        <x:v>PRP128</x:v>
+      </x:c>
+      <x:c r="F324" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G324" s="63" t="str">
+        <x:v>SHILPI RUCHI KERKETTA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" ht="15" hidden="0" customHeight="1">
+      <x:c r="A325" s="61" t="str">
+        <x:v>BECE102L</x:v>
+      </x:c>
+      <x:c r="B325" s="62" t="str">
+        <x:v>Digital Systems Design</x:v>
+      </x:c>
+      <x:c r="C325" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D325" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E325" s="62" t="str">
+        <x:v>PRP127</x:v>
+      </x:c>
+      <x:c r="F325" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G325" s="63" t="str">
+        <x:v>SHILPI RUCHI KERKETTA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" ht="15" hidden="0" customHeight="1">
+      <x:c r="A326" s="61" t="str">
+        <x:v>BECE102P</x:v>
+      </x:c>
+      <x:c r="B326" s="62" t="str">
+        <x:v>Digital Systems Design Lab</x:v>
+      </x:c>
+      <x:c r="C326" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D326" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E326" s="62" t="str">
+        <x:v>SJT516</x:v>
+      </x:c>
+      <x:c r="F326" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G326" s="63" t="str">
+        <x:v>SHILPI RUCHI KERKETTA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" ht="15" hidden="0" customHeight="1">
+      <x:c r="A327" s="61" t="str">
+        <x:v>BECE102P</x:v>
+      </x:c>
+      <x:c r="B327" s="62" t="str">
+        <x:v>Digital Systems Design Lab</x:v>
+      </x:c>
+      <x:c r="C327" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D327" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E327" s="62" t="str">
+        <x:v>SJT516</x:v>
+      </x:c>
+      <x:c r="F327" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G327" s="63" t="str">
+        <x:v>SHILPI RUCHI KERKETTA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" ht="15" hidden="0" customHeight="1">
+      <x:c r="A328" s="61" t="str">
+        <x:v>BECE204L</x:v>
+      </x:c>
+      <x:c r="B328" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers</x:v>
+      </x:c>
+      <x:c r="C328" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D328" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E328" s="62" t="str">
+        <x:v>PRP238</x:v>
+      </x:c>
+      <x:c r="F328" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G328" s="63" t="str">
+        <x:v>ABDUL RAHIM VC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" ht="15" hidden="0" customHeight="1">
+      <x:c r="A329" s="61" t="str">
+        <x:v>BECE204L</x:v>
+      </x:c>
+      <x:c r="B329" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers</x:v>
+      </x:c>
+      <x:c r="C329" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D329" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E329" s="62" t="str">
+        <x:v>PRP134</x:v>
+      </x:c>
+      <x:c r="F329" s="62" t="str">
+        <x:v>F2+TF2</x:v>
+      </x:c>
+      <x:c r="G329" s="63" t="str">
+        <x:v>ABDUL RAHIM VC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" ht="15" hidden="0" customHeight="1">
+      <x:c r="A330" s="61" t="str">
+        <x:v>BECE204L</x:v>
+      </x:c>
+      <x:c r="B330" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers</x:v>
+      </x:c>
+      <x:c r="C330" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D330" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E330" s="62" t="str">
+        <x:v>PRP134</x:v>
+      </x:c>
+      <x:c r="F330" s="62" t="str">
+        <x:v>F1+TF1</x:v>
+      </x:c>
+      <x:c r="G330" s="63" t="str">
+        <x:v>PRIYANKA S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" ht="15" hidden="0" customHeight="1">
+      <x:c r="A331" s="61" t="str">
+        <x:v>BECE204P</x:v>
+      </x:c>
+      <x:c r="B331" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers Lab</x:v>
+      </x:c>
+      <x:c r="C331" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D331" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E331" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F331" s="62" t="str">
+        <x:v>L11+L12</x:v>
+      </x:c>
+      <x:c r="G331" s="63" t="str">
+        <x:v>ABDUL RAHIM VC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" ht="15" hidden="0" customHeight="1">
+      <x:c r="A332" s="61" t="str">
+        <x:v>BECE204P</x:v>
+      </x:c>
+      <x:c r="B332" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers Lab</x:v>
+      </x:c>
+      <x:c r="C332" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D332" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E332" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F332" s="62" t="str">
+        <x:v>L41+L42</x:v>
+      </x:c>
+      <x:c r="G332" s="63" t="str">
+        <x:v>PRIYANKA S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" ht="15" hidden="0" customHeight="1">
+      <x:c r="A333" s="61" t="str">
+        <x:v>BECE204P</x:v>
+      </x:c>
+      <x:c r="B333" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers Lab</x:v>
+      </x:c>
+      <x:c r="C333" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D333" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E333" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F333" s="62" t="str">
+        <x:v>L43+L44</x:v>
+      </x:c>
+      <x:c r="G333" s="63" t="str">
+        <x:v>PRIYANKA S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" ht="15" hidden="0" customHeight="1">
+      <x:c r="A334" s="61" t="str">
+        <x:v>BECE204P</x:v>
+      </x:c>
+      <x:c r="B334" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers Lab</x:v>
+      </x:c>
+      <x:c r="C334" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D334" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E334" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F334" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G334" s="63" t="str">
+        <x:v>ABDUL RAHIM VC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" ht="15" hidden="0" customHeight="1">
+      <x:c r="A335" s="61" t="str">
+        <x:v>BECE204P</x:v>
+      </x:c>
+      <x:c r="B335" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers Lab</x:v>
+      </x:c>
+      <x:c r="C335" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D335" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E335" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F335" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G335" s="63" t="str">
+        <x:v>ABDUL RAHIM VC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" ht="15" hidden="0" customHeight="1">
+      <x:c r="A336" s="61" t="str">
+        <x:v>BECE204P</x:v>
+      </x:c>
+      <x:c r="B336" s="62" t="str">
+        <x:v>Microprocessors and Microcontrollers Lab</x:v>
+      </x:c>
+      <x:c r="C336" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D336" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E336" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F336" s="62" t="str">
+        <x:v>L55+L56</x:v>
+      </x:c>
+      <x:c r="G336" s="63" t="str">
+        <x:v>ABDUL RAHIM VC</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" ht="15" hidden="0" customHeight="1">
+      <x:c r="A337" s="61" t="str">
+        <x:v>BECE207L</x:v>
+      </x:c>
+      <x:c r="B337" s="62" t="str">
+        <x:v>Random Processes</x:v>
+      </x:c>
+      <x:c r="C337" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D337" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E337" s="62" t="str">
+        <x:v>TT304</x:v>
+      </x:c>
+      <x:c r="F337" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G337" s="63" t="str">
+        <x:v>ASHISH P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" ht="15" hidden="0" customHeight="1">
+      <x:c r="A338" s="61" t="str">
+        <x:v>BECE301L</x:v>
+      </x:c>
+      <x:c r="B338" s="62" t="str">
+        <x:v>Digital Signal Processing</x:v>
+      </x:c>
+      <x:c r="C338" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D338" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E338" s="62" t="str">
+        <x:v>TT630</x:v>
+      </x:c>
+      <x:c r="F338" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G338" s="63" t="str">
+        <x:v>VALARMATHI J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" ht="15" hidden="0" customHeight="1">
+      <x:c r="A339" s="61" t="str">
+        <x:v>BECE301P</x:v>
+      </x:c>
+      <x:c r="B339" s="62" t="str">
+        <x:v>Digital Signal Processing Lab</x:v>
+      </x:c>
+      <x:c r="C339" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D339" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E339" s="62" t="str">
+        <x:v>TT232</x:v>
+      </x:c>
+      <x:c r="F339" s="62" t="str">
+        <x:v>L37+L38</x:v>
+      </x:c>
+      <x:c r="G339" s="63" t="str">
+        <x:v>VALARMATHI J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" ht="15" hidden="0" customHeight="1">
+      <x:c r="A340" s="61" t="str">
+        <x:v>BECE301P</x:v>
+      </x:c>
+      <x:c r="B340" s="62" t="str">
+        <x:v>Digital Signal Processing Lab</x:v>
+      </x:c>
+      <x:c r="C340" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D340" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E340" s="62" t="str">
+        <x:v>TT232</x:v>
+      </x:c>
+      <x:c r="F340" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G340" s="63" t="str">
+        <x:v>VALARMATHI J</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" ht="15" hidden="0" customHeight="1">
+      <x:c r="A341" s="61" t="str">
+        <x:v>BECE302L</x:v>
+      </x:c>
+      <x:c r="B341" s="62" t="str">
+        <x:v>Control Systems</x:v>
+      </x:c>
+      <x:c r="C341" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D341" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E341" s="62" t="str">
+        <x:v>TT531A</x:v>
+      </x:c>
+      <x:c r="F341" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G341" s="63" t="str">
+        <x:v>VELMURUGAN V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" ht="15" hidden="0" customHeight="1">
+      <x:c r="A342" s="61" t="str">
+        <x:v>BECE304L</x:v>
+      </x:c>
+      <x:c r="B342" s="62" t="str">
+        <x:v>Analog Communication Systems</x:v>
+      </x:c>
+      <x:c r="C342" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D342" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E342" s="62" t="str">
+        <x:v>TT530A</x:v>
+      </x:c>
+      <x:c r="F342" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G342" s="63" t="str">
+        <x:v>KAVITHA K.V.N.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" ht="15" hidden="0" customHeight="1">
+      <x:c r="A343" s="61" t="str">
+        <x:v>BECE304P</x:v>
+      </x:c>
+      <x:c r="B343" s="62" t="str">
+        <x:v>Analog Communication Systems Lab</x:v>
+      </x:c>
+      <x:c r="C343" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D343" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E343" s="62" t="str">
+        <x:v>TT135</x:v>
+      </x:c>
+      <x:c r="F343" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G343" s="63" t="str">
+        <x:v>KAVITHA K.V.N.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" ht="15" hidden="0" customHeight="1">
+      <x:c r="A344" s="61" t="str">
+        <x:v>BECE304P</x:v>
+      </x:c>
+      <x:c r="B344" s="62" t="str">
+        <x:v>Analog Communication Systems Lab</x:v>
+      </x:c>
+      <x:c r="C344" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D344" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E344" s="62" t="str">
+        <x:v>TT135</x:v>
+      </x:c>
+      <x:c r="F344" s="62" t="str">
+        <x:v>L55+L56</x:v>
+      </x:c>
+      <x:c r="G344" s="63" t="str">
+        <x:v>KAVITHA K.V.N.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" ht="15" hidden="0" customHeight="1">
+      <x:c r="A345" s="61" t="str">
+        <x:v>BECE305L</x:v>
+      </x:c>
+      <x:c r="B345" s="62" t="str">
+        <x:v>Antenna and Microwave Engineering</x:v>
+      </x:c>
+      <x:c r="C345" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D345" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E345" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F345" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G345" s="63" t="str">
+        <x:v>SHAMBAVI K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" ht="15" hidden="0" customHeight="1">
+      <x:c r="A346" s="61" t="str">
+        <x:v>BECE305P</x:v>
+      </x:c>
+      <x:c r="B346" s="62" t="str">
+        <x:v>Antenna and Microwave Engineering Lab</x:v>
+      </x:c>
+      <x:c r="C346" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D346" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E346" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F346" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G346" s="63" t="str">
+        <x:v>SHAMBAVI K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" ht="15" hidden="0" customHeight="1">
+      <x:c r="A347" s="61" t="str">
+        <x:v>BECE305P</x:v>
+      </x:c>
+      <x:c r="B347" s="62" t="str">
+        <x:v>Antenna and Microwave Engineering Lab</x:v>
+      </x:c>
+      <x:c r="C347" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D347" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E347" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F347" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G347" s="63" t="str">
+        <x:v>SHAMBAVI K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" ht="15" hidden="0" customHeight="1">
+      <x:c r="A348" s="61" t="str">
+        <x:v>BECE306L</x:v>
+      </x:c>
+      <x:c r="B348" s="62" t="str">
+        <x:v>Digital Communication Systems</x:v>
+      </x:c>
+      <x:c r="C348" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D348" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E348" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F348" s="62" t="str">
+        <x:v>G2+TG2</x:v>
+      </x:c>
+      <x:c r="G348" s="63" t="str">
+        <x:v>KAVITHA K.V.N.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" ht="15" hidden="0" customHeight="1">
+      <x:c r="A349" s="61" t="str">
+        <x:v>BECE306P</x:v>
+      </x:c>
+      <x:c r="B349" s="62" t="str">
+        <x:v>Digital Communication Systems Lab</x:v>
+      </x:c>
+      <x:c r="C349" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D349" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E349" s="62" t="str">
+        <x:v>TT135</x:v>
+      </x:c>
+      <x:c r="F349" s="62" t="str">
+        <x:v>L11+L12</x:v>
+      </x:c>
+      <x:c r="G349" s="63" t="str">
+        <x:v>KAVITHA K.V.N.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" ht="15" hidden="0" customHeight="1">
+      <x:c r="A350" s="61" t="str">
+        <x:v>BECE306P</x:v>
+      </x:c>
+      <x:c r="B350" s="62" t="str">
+        <x:v>Digital Communication Systems Lab</x:v>
+      </x:c>
+      <x:c r="C350" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D350" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E350" s="62" t="str">
+        <x:v>TT135</x:v>
+      </x:c>
+      <x:c r="F350" s="62" t="str">
+        <x:v>L25+L26</x:v>
+      </x:c>
+      <x:c r="G350" s="63" t="str">
+        <x:v>KAVITHA K.V.N.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" ht="15" hidden="0" customHeight="1">
+      <x:c r="A351" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B351" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C351" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D351" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E351" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F351" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G351" s="63" t="str">
+        <x:v>VIVEK RAJPOOT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" ht="15" hidden="0" customHeight="1">
+      <x:c r="A352" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B352" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C352" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D352" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E352" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F352" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G352" s="63" t="str">
+        <x:v>PRAKASAM P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" ht="15" hidden="0" customHeight="1">
+      <x:c r="A353" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B353" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C353" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D353" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E353" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F353" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G353" s="63" t="str">
+        <x:v>ABHIJIT BHOWMICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" ht="15" hidden="0" customHeight="1">
+      <x:c r="A354" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B354" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C354" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D354" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E354" s="62" t="str">
+        <x:v>TT302</x:v>
+      </x:c>
+      <x:c r="F354" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G354" s="63" t="str">
+        <x:v>VEERAPU GOUTHAM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" ht="15" hidden="0" customHeight="1">
+      <x:c r="A355" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B355" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C355" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D355" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E355" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F355" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G355" s="63" t="str">
+        <x:v>BUDHADITYA BHATTACHARYYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" ht="15" hidden="0" customHeight="1">
+      <x:c r="A356" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B356" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C356" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D356" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E356" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F356" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G356" s="63" t="str">
+        <x:v>VIVEK RAJPOOT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" ht="15" hidden="0" customHeight="1">
+      <x:c r="A357" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B357" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C357" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D357" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E357" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F357" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G357" s="63" t="str">
+        <x:v>ASWATHI V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" ht="15" hidden="0" customHeight="1">
+      <x:c r="A358" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B358" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C358" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D358" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E358" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F358" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G358" s="63" t="str">
+        <x:v>ASWATHI V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" ht="15" hidden="0" customHeight="1">
+      <x:c r="A359" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B359" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C359" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D359" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E359" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F359" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G359" s="63" t="str">
+        <x:v>ABHIJIT BHOWMICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" ht="15" hidden="0" customHeight="1">
+      <x:c r="A360" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B360" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C360" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D360" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E360" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F360" s="62" t="str">
+        <x:v>C1+TC1</x:v>
+      </x:c>
+      <x:c r="G360" s="63" t="str">
+        <x:v>SUDHANSHU ARYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" ht="15" hidden="0" customHeight="1">
+      <x:c r="A361" s="61" t="str">
+        <x:v>BECE317L</x:v>
+      </x:c>
+      <x:c r="B361" s="62" t="str">
+        <x:v>Wireless and Mobile Communications</x:v>
+      </x:c>
+      <x:c r="C361" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D361" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E361" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F361" s="62" t="str">
+        <x:v>C2+TC2</x:v>
+      </x:c>
+      <x:c r="G361" s="63" t="str">
+        <x:v>SUDHANSHU ARYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" ht="15" hidden="0" customHeight="1">
+      <x:c r="A362" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B362" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C362" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D362" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E362" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F362" s="62" t="str">
+        <x:v>L33+L34</x:v>
+      </x:c>
+      <x:c r="G362" s="63" t="str">
+        <x:v>PRAKASAM P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" ht="15" hidden="0" customHeight="1">
+      <x:c r="A363" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B363" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C363" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D363" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E363" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F363" s="62" t="str">
+        <x:v>L1+L2</x:v>
+      </x:c>
+      <x:c r="G363" s="63" t="str">
+        <x:v>ABHIJIT BHOWMICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" ht="15" hidden="0" customHeight="1">
+      <x:c r="A364" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B364" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C364" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D364" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E364" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F364" s="62" t="str">
+        <x:v>L37+L38</x:v>
+      </x:c>
+      <x:c r="G364" s="63" t="str">
+        <x:v>ABHIJIT BHOWMICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" ht="15" hidden="0" customHeight="1">
+      <x:c r="A365" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B365" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C365" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D365" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E365" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F365" s="62" t="str">
+        <x:v>L39+L40</x:v>
+      </x:c>
+      <x:c r="G365" s="63" t="str">
+        <x:v>PRAKASAM P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" ht="15" hidden="0" customHeight="1">
+      <x:c r="A366" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B366" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C366" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D366" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E366" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F366" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G366" s="63" t="str">
+        <x:v>ABHIJIT BHOWMICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" ht="15" hidden="0" customHeight="1">
+      <x:c r="A367" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B367" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C367" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D367" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E367" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F367" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G367" s="63" t="str">
+        <x:v>VIVEK RAJPOOT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" ht="15" hidden="0" customHeight="1">
+      <x:c r="A368" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B368" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C368" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D368" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E368" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F368" s="62" t="str">
+        <x:v>L27+L28</x:v>
+      </x:c>
+      <x:c r="G368" s="63" t="str">
+        <x:v>BUDHADITYA BHATTACHARYYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" ht="15" hidden="0" customHeight="1">
+      <x:c r="A369" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B369" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C369" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D369" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E369" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F369" s="62" t="str">
+        <x:v>L29+L30</x:v>
+      </x:c>
+      <x:c r="G369" s="63" t="str">
+        <x:v>ABHIJIT BHOWMICK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" ht="15" hidden="0" customHeight="1">
+      <x:c r="A370" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B370" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C370" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D370" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E370" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F370" s="62" t="str">
+        <x:v>L13+L14</x:v>
+      </x:c>
+      <x:c r="G370" s="63" t="str">
+        <x:v>BUDHADITYA BHATTACHARYYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="15" hidden="0" customHeight="1">
+      <x:c r="A371" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B371" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C371" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D371" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E371" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F371" s="62" t="str">
+        <x:v>L29+L30</x:v>
+      </x:c>
+      <x:c r="G371" s="63" t="str">
+        <x:v>SUDHANSHU ARYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="15" hidden="0" customHeight="1">
+      <x:c r="A372" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B372" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C372" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D372" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E372" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F372" s="62" t="str">
+        <x:v>L3+L4</x:v>
+      </x:c>
+      <x:c r="G372" s="63" t="str">
+        <x:v>VIVEK RAJPOOT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="15" hidden="0" customHeight="1">
+      <x:c r="A373" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B373" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C373" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D373" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E373" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F373" s="62" t="str">
+        <x:v>L7+L8</x:v>
+      </x:c>
+      <x:c r="G373" s="63" t="str">
+        <x:v>VIVEK RAJPOOT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="15" hidden="0" customHeight="1">
+      <x:c r="A374" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B374" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C374" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D374" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E374" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F374" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G374" s="63" t="str">
+        <x:v>VIVEK RAJPOOT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="15" hidden="0" customHeight="1">
+      <x:c r="A375" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B375" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C375" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D375" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E375" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F375" s="62" t="str">
+        <x:v>L35+L36</x:v>
+      </x:c>
+      <x:c r="G375" s="63" t="str">
+        <x:v>ASWATHI V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="15" hidden="0" customHeight="1">
+      <x:c r="A376" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B376" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C376" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D376" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E376" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F376" s="62" t="str">
+        <x:v>L37+L38</x:v>
+      </x:c>
+      <x:c r="G376" s="63" t="str">
+        <x:v>ASWATHI V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="15" hidden="0" customHeight="1">
+      <x:c r="A377" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B377" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C377" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D377" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E377" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F377" s="62" t="str">
+        <x:v>L19+L20</x:v>
+      </x:c>
+      <x:c r="G377" s="63" t="str">
+        <x:v>SUDHANSHU ARYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="15" hidden="0" customHeight="1">
+      <x:c r="A378" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B378" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C378" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D378" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E378" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F378" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G378" s="63" t="str">
+        <x:v>SUDHANSHU ARYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="15" hidden="0" customHeight="1">
+      <x:c r="A379" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B379" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C379" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D379" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E379" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F379" s="62" t="str">
+        <x:v>L47+L48</x:v>
+      </x:c>
+      <x:c r="G379" s="63" t="str">
+        <x:v>SUDHANSHU ARYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="15" hidden="0" customHeight="1">
+      <x:c r="A380" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B380" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C380" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D380" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E380" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F380" s="62" t="str">
+        <x:v>L5+L6</x:v>
+      </x:c>
+      <x:c r="G380" s="63" t="str">
+        <x:v>ASWATHI V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="15" hidden="0" customHeight="1">
+      <x:c r="A381" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B381" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C381" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D381" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E381" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F381" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G381" s="63" t="str">
+        <x:v>ASWATHI V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="15" hidden="0" customHeight="1">
+      <x:c r="A382" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B382" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C382" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D382" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E382" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F382" s="62" t="str">
+        <x:v>L33+L34</x:v>
+      </x:c>
+      <x:c r="G382" s="63" t="str">
+        <x:v>VEERAPU GOUTHAM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="15" hidden="0" customHeight="1">
+      <x:c r="A383" s="61" t="str">
+        <x:v>BECE317P</x:v>
+      </x:c>
+      <x:c r="B383" s="62" t="str">
+        <x:v>Wireless and Mobile Communications Lab</x:v>
+      </x:c>
+      <x:c r="C383" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D383" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E383" s="62" t="str">
+        <x:v>PRP108</x:v>
+      </x:c>
+      <x:c r="F383" s="62" t="str">
+        <x:v>L59+L60</x:v>
+      </x:c>
+      <x:c r="G383" s="63" t="str">
+        <x:v>VEERAPU GOUTHAM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="15" hidden="0" customHeight="1">
+      <x:c r="A384" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B384" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C384" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D384" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E384" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F384" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G384" s="63" t="str">
+        <x:v>RAJALAKSHMI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="15" hidden="0" customHeight="1">
+      <x:c r="A385" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B385" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C385" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D385" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E385" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F385" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G385" s="63" t="str">
+        <x:v>SUBHRA SANKHA SARMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="15" hidden="0" customHeight="1">
+      <x:c r="A386" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B386" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C386" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D386" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E386" s="62" t="str">
+        <x:v>TT303</x:v>
+      </x:c>
+      <x:c r="F386" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G386" s="63" t="str">
+        <x:v>SANJAY KUMAR SINGH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="15" hidden="0" customHeight="1">
+      <x:c r="A387" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B387" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C387" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D387" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E387" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F387" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G387" s="63" t="str">
+        <x:v>REVATHI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="15" hidden="0" customHeight="1">
+      <x:c r="A388" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B388" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C388" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D388" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E388" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F388" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G388" s="63" t="str">
+        <x:v>RAJALAKSHMI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="15" hidden="0" customHeight="1">
+      <x:c r="A389" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B389" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C389" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D389" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E389" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F389" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G389" s="63" t="str">
+        <x:v>SANGEETHA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="15" hidden="0" customHeight="1">
+      <x:c r="A390" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B390" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C390" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D390" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E390" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F390" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G390" s="63" t="str">
+        <x:v>MANISH KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="15" hidden="0" customHeight="1">
+      <x:c r="A391" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B391" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C391" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D391" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E391" s="62" t="str">
+        <x:v>TT302</x:v>
+      </x:c>
+      <x:c r="F391" s="62" t="str">
+        <x:v>A1+TA1</x:v>
+      </x:c>
+      <x:c r="G391" s="63" t="str">
+        <x:v>AARTHI G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="15" hidden="0" customHeight="1">
+      <x:c r="A392" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B392" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C392" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D392" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E392" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F392" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G392" s="63" t="str">
+        <x:v>SANGEETHA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="15" hidden="0" customHeight="1">
+      <x:c r="A393" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B393" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C393" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D393" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E393" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F393" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G393" s="63" t="str">
+        <x:v>SANJAY KUMAR SINGH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="15" hidden="0" customHeight="1">
+      <x:c r="A394" s="61" t="str">
+        <x:v>BECE318L</x:v>
+      </x:c>
+      <x:c r="B394" s="62" t="str">
+        <x:v>Optical Fiber Communications</x:v>
+      </x:c>
+      <x:c r="C394" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D394" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E394" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F394" s="62" t="str">
+        <x:v>A2+TA2</x:v>
+      </x:c>
+      <x:c r="G394" s="63" t="str">
+        <x:v>AARTHI G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="15" hidden="0" customHeight="1">
+      <x:c r="A395" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B395" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C395" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D395" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E395" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F395" s="62" t="str">
+        <x:v>L47+L48</x:v>
+      </x:c>
+      <x:c r="G395" s="63" t="str">
+        <x:v>AARTHI G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="15" hidden="0" customHeight="1">
+      <x:c r="A396" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B396" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C396" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D396" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E396" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F396" s="62" t="str">
+        <x:v>L7+L8</x:v>
+      </x:c>
+      <x:c r="G396" s="63" t="str">
+        <x:v>RAJALAKSHMI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="15" hidden="0" customHeight="1">
+      <x:c r="A397" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B397" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C397" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D397" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E397" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F397" s="62" t="str">
+        <x:v>L37+L38</x:v>
+      </x:c>
+      <x:c r="G397" s="63" t="str">
+        <x:v>RAJALAKSHMI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="15" hidden="0" customHeight="1">
+      <x:c r="A398" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B398" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C398" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D398" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E398" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F398" s="62" t="str">
+        <x:v>L25+L26</x:v>
+      </x:c>
+      <x:c r="G398" s="63" t="str">
+        <x:v>SANJAY KUMAR SINGH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="15" hidden="0" customHeight="1">
+      <x:c r="A399" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B399" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C399" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D399" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E399" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F399" s="62" t="str">
+        <x:v>L29+L30</x:v>
+      </x:c>
+      <x:c r="G399" s="63" t="str">
+        <x:v>SANGEETHA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="15" hidden="0" customHeight="1">
+      <x:c r="A400" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B400" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C400" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D400" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E400" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F400" s="62" t="str">
+        <x:v>L33+L34</x:v>
+      </x:c>
+      <x:c r="G400" s="63" t="str">
+        <x:v>SANGEETHA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="15" hidden="0" customHeight="1">
+      <x:c r="A401" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B401" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C401" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D401" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E401" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F401" s="62" t="str">
+        <x:v>L11+L12</x:v>
+      </x:c>
+      <x:c r="G401" s="63" t="str">
+        <x:v>AARTHI G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="15" hidden="0" customHeight="1">
+      <x:c r="A402" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B402" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C402" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D402" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E402" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F402" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G402" s="63" t="str">
+        <x:v>SANJAY KUMAR SINGH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="15" hidden="0" customHeight="1">
+      <x:c r="A403" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B403" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C403" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D403" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E403" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F403" s="62" t="str">
+        <x:v>L3+L4</x:v>
+      </x:c>
+      <x:c r="G403" s="63" t="str">
+        <x:v>AARTHI G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="15" hidden="0" customHeight="1">
+      <x:c r="A404" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B404" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C404" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D404" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E404" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F404" s="62" t="str">
+        <x:v>L5+L6</x:v>
+      </x:c>
+      <x:c r="G404" s="63" t="str">
+        <x:v>RAJALAKSHMI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="15" hidden="0" customHeight="1">
+      <x:c r="A405" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B405" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C405" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D405" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E405" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F405" s="62" t="str">
+        <x:v>L59+L60</x:v>
+      </x:c>
+      <x:c r="G405" s="63" t="str">
+        <x:v>RAJALAKSHMI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="15" hidden="0" customHeight="1">
+      <x:c r="A406" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B406" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C406" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D406" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E406" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F406" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G406" s="63" t="str">
+        <x:v>SANGEETHA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="15" hidden="0" customHeight="1">
+      <x:c r="A407" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B407" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C407" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D407" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E407" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F407" s="62" t="str">
+        <x:v>L41+L42</x:v>
+      </x:c>
+      <x:c r="G407" s="63" t="str">
+        <x:v>SANGEETHA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="15" hidden="0" customHeight="1">
+      <x:c r="A408" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B408" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C408" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D408" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E408" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F408" s="62" t="str">
+        <x:v>L39+L40</x:v>
+      </x:c>
+      <x:c r="G408" s="63" t="str">
+        <x:v>AARTHI G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="15" hidden="0" customHeight="1">
+      <x:c r="A409" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B409" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C409" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D409" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E409" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F409" s="62" t="str">
+        <x:v>L35+L36</x:v>
+      </x:c>
+      <x:c r="G409" s="63" t="str">
+        <x:v>SANJAY KUMAR SINGH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="15" hidden="0" customHeight="1">
+      <x:c r="A410" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B410" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C410" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D410" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E410" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F410" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G410" s="63" t="str">
+        <x:v>SANJAY KUMAR SINGH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="15" hidden="0" customHeight="1">
+      <x:c r="A411" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B411" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C411" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D411" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E411" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F411" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G411" s="63" t="str">
+        <x:v>REVATHI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="15" hidden="0" customHeight="1">
+      <x:c r="A412" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B412" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C412" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D412" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E412" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F412" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G412" s="63" t="str">
+        <x:v>SUBHRA SANKHA SARMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="15" hidden="0" customHeight="1">
+      <x:c r="A413" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B413" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C413" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D413" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E413" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F413" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G413" s="63" t="str">
+        <x:v>SUBHRA SANKHA SARMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="15" hidden="0" customHeight="1">
+      <x:c r="A414" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B414" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C414" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D414" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E414" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F414" s="62" t="str">
+        <x:v>L43+L44</x:v>
+      </x:c>
+      <x:c r="G414" s="63" t="str">
+        <x:v>REVATHI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="15" hidden="0" customHeight="1">
+      <x:c r="A415" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B415" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C415" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D415" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E415" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F415" s="62" t="str">
+        <x:v>L13+L14</x:v>
+      </x:c>
+      <x:c r="G415" s="63" t="str">
+        <x:v>MANISH KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="15" hidden="0" customHeight="1">
+      <x:c r="A416" s="61" t="str">
+        <x:v>BECE318P</x:v>
+      </x:c>
+      <x:c r="B416" s="62" t="str">
+        <x:v>Optical Fiber Communications Lab</x:v>
+      </x:c>
+      <x:c r="C416" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D416" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E416" s="62" t="str">
+        <x:v>TT144</x:v>
+      </x:c>
+      <x:c r="F416" s="62" t="str">
+        <x:v>L27+L28</x:v>
+      </x:c>
+      <x:c r="G416" s="63" t="str">
+        <x:v>MANISH KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="15" hidden="0" customHeight="1">
+      <x:c r="A417" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B417" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C417" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D417" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E417" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F417" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G417" s="63" t="str">
+        <x:v>VELMURUGAN T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="15" hidden="0" customHeight="1">
+      <x:c r="A418" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B418" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C418" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D418" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E418" s="62" t="str">
+        <x:v>TT302</x:v>
+      </x:c>
+      <x:c r="F418" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G418" s="63" t="str">
+        <x:v>PREETHA K.S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="15" hidden="0" customHeight="1">
+      <x:c r="A419" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B419" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C419" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D419" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E419" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F419" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G419" s="63" t="str">
+        <x:v>DEEPIKA RANI SONA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="15" hidden="0" customHeight="1">
+      <x:c r="A420" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B420" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C420" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D420" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E420" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F420" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G420" s="63" t="str">
+        <x:v>NANDAKUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="15" hidden="0" customHeight="1">
+      <x:c r="A421" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B421" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C421" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D421" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E421" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F421" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G421" s="63" t="str">
+        <x:v>DEEPIKA RANI SONA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="15" hidden="0" customHeight="1">
+      <x:c r="A422" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B422" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C422" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D422" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E422" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F422" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G422" s="63" t="str">
+        <x:v>TANMAYA KUMAR DAS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="15" hidden="0" customHeight="1">
+      <x:c r="A423" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B423" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C423" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D423" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E423" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F423" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G423" s="63" t="str">
+        <x:v>RENUGA DEVI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="15" hidden="0" customHeight="1">
+      <x:c r="A424" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B424" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C424" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D424" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E424" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F424" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G424" s="63" t="str">
+        <x:v>VELMURUGAN T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="15" hidden="0" customHeight="1">
+      <x:c r="A425" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B425" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C425" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D425" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E425" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F425" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G425" s="63" t="str">
+        <x:v>NANDAKUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="15" hidden="0" customHeight="1">
+      <x:c r="A426" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B426" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C426" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D426" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E426" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F426" s="62" t="str">
+        <x:v>B1+TB1</x:v>
+      </x:c>
+      <x:c r="G426" s="63" t="str">
+        <x:v>RAVI KUMAR C V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="15" hidden="0" customHeight="1">
+      <x:c r="A427" s="61" t="str">
+        <x:v>BECE401L</x:v>
+      </x:c>
+      <x:c r="B427" s="62" t="str">
+        <x:v>Computer Communications and Networks</x:v>
+      </x:c>
+      <x:c r="C427" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D427" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E427" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F427" s="62" t="str">
+        <x:v>B2+TB2</x:v>
+      </x:c>
+      <x:c r="G427" s="63" t="str">
+        <x:v>RAVI KUMAR C V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="15" hidden="0" customHeight="1">
+      <x:c r="A428" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B428" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C428" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D428" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E428" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F428" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G428" s="63" t="str">
+        <x:v>VELMURUGAN T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="15" hidden="0" customHeight="1">
+      <x:c r="A429" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B429" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C429" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D429" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E429" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F429" s="62" t="str">
+        <x:v>L55+L56</x:v>
+      </x:c>
+      <x:c r="G429" s="63" t="str">
+        <x:v>VELMURUGAN T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="15" hidden="0" customHeight="1">
+      <x:c r="A430" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B430" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C430" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D430" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E430" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F430" s="62" t="str">
+        <x:v>L11+L12</x:v>
+      </x:c>
+      <x:c r="G430" s="63" t="str">
+        <x:v>NANDAKUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="15" hidden="0" customHeight="1">
+      <x:c r="A431" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B431" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C431" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D431" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E431" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F431" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G431" s="63" t="str">
+        <x:v>VELMURUGAN T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="15" hidden="0" customHeight="1">
+      <x:c r="A432" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B432" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C432" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D432" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E432" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F432" s="62" t="str">
+        <x:v>L13+L14</x:v>
+      </x:c>
+      <x:c r="G432" s="63" t="str">
+        <x:v>NANDAKUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="15" hidden="0" customHeight="1">
+      <x:c r="A433" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B433" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C433" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D433" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E433" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F433" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G433" s="63" t="str">
+        <x:v>NANDAKUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="15" hidden="0" customHeight="1">
+      <x:c r="A434" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B434" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C434" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D434" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E434" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F434" s="62" t="str">
+        <x:v>L25+L26</x:v>
+      </x:c>
+      <x:c r="G434" s="63" t="str">
+        <x:v>VELMURUGAN T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="15" hidden="0" customHeight="1">
+      <x:c r="A435" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B435" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C435" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D435" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E435" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F435" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G435" s="63" t="str">
+        <x:v>DEEPIKA RANI SONA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="15" hidden="0" customHeight="1">
+      <x:c r="A436" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B436" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C436" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D436" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E436" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F436" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G436" s="63" t="str">
+        <x:v>NANDAKUMAR S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="15" hidden="0" customHeight="1">
+      <x:c r="A437" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B437" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C437" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D437" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E437" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F437" s="62" t="str">
+        <x:v>L39+L40</x:v>
+      </x:c>
+      <x:c r="G437" s="63" t="str">
+        <x:v>DEEPIKA RANI SONA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="15" hidden="0" customHeight="1">
+      <x:c r="A438" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B438" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C438" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D438" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E438" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F438" s="62" t="str">
+        <x:v>L47+L48</x:v>
+      </x:c>
+      <x:c r="G438" s="63" t="str">
+        <x:v>DEEPIKA RANI SONA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="15" hidden="0" customHeight="1">
+      <x:c r="A439" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B439" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C439" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D439" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E439" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F439" s="62" t="str">
+        <x:v>L27+L28</x:v>
+      </x:c>
+      <x:c r="G439" s="63" t="str">
+        <x:v>RAVI KUMAR C V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="15" hidden="0" customHeight="1">
+      <x:c r="A440" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B440" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C440" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D440" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E440" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F440" s="62" t="str">
+        <x:v>L21+L22</x:v>
+      </x:c>
+      <x:c r="G440" s="63" t="str">
+        <x:v>RENUGA DEVI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" ht="15" hidden="0" customHeight="1">
+      <x:c r="A441" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B441" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C441" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D441" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E441" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F441" s="62" t="str">
+        <x:v>L53+L54</x:v>
+      </x:c>
+      <x:c r="G441" s="63" t="str">
+        <x:v>TANMAYA KUMAR DAS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="15" hidden="0" customHeight="1">
+      <x:c r="A442" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B442" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C442" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D442" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E442" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F442" s="62" t="str">
+        <x:v>L23+L24</x:v>
+      </x:c>
+      <x:c r="G442" s="63" t="str">
+        <x:v>DEEPIKA RANI SONA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" ht="15" hidden="0" customHeight="1">
+      <x:c r="A443" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B443" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C443" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D443" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E443" s="62" t="str">
+        <x:v>TT145</x:v>
+      </x:c>
+      <x:c r="F443" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G443" s="63" t="str">
+        <x:v>RAVI KUMAR C V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" ht="15" hidden="0" customHeight="1">
+      <x:c r="A444" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B444" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C444" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D444" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E444" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F444" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G444" s="63" t="str">
+        <x:v>PREETHA K.S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" ht="15" hidden="0" customHeight="1">
+      <x:c r="A445" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B445" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C445" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D445" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E445" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F445" s="62" t="str">
+        <x:v>L41+L42</x:v>
+      </x:c>
+      <x:c r="G445" s="63" t="str">
+        <x:v>RAVI KUMAR C V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" ht="15" hidden="0" customHeight="1">
+      <x:c r="A446" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B446" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C446" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D446" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E446" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F446" s="62" t="str">
+        <x:v>L43+L44</x:v>
+      </x:c>
+      <x:c r="G446" s="63" t="str">
+        <x:v>RAVI KUMAR C V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" ht="15" hidden="0" customHeight="1">
+      <x:c r="A447" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B447" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C447" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D447" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E447" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F447" s="62" t="str">
+        <x:v>L3+L4</x:v>
+      </x:c>
+      <x:c r="G447" s="63" t="str">
+        <x:v>RENUGA DEVI S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" ht="15" hidden="0" customHeight="1">
+      <x:c r="A448" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B448" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C448" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D448" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E448" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F448" s="62" t="str">
+        <x:v>L35+L36</x:v>
+      </x:c>
+      <x:c r="G448" s="63" t="str">
+        <x:v>PREETHA K.S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" ht="15" hidden="0" customHeight="1">
+      <x:c r="A449" s="61" t="str">
+        <x:v>BECE401P</x:v>
+      </x:c>
+      <x:c r="B449" s="62" t="str">
+        <x:v>Computer Communications and Networks Lab</x:v>
+      </x:c>
+      <x:c r="C449" s="62" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="D449" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E449" s="62" t="str">
+        <x:v>TT134</x:v>
+      </x:c>
+      <x:c r="F449" s="62" t="str">
+        <x:v>L37+L38</x:v>
+      </x:c>
+      <x:c r="G449" s="63" t="str">
+        <x:v>TANMAYA KUMAR DAS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" ht="15" hidden="0" customHeight="1">
+      <x:c r="A450" s="61" t="str">
+        <x:v>BECE309L</x:v>
+      </x:c>
+      <x:c r="B450" s="62" t="str">
+        <x:v>Artificial Intelligence and Machine Learning</x:v>
+      </x:c>
+      <x:c r="C450" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D450" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E450" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F450" s="62" t="str">
+        <x:v>G2+TG2</x:v>
+      </x:c>
+      <x:c r="G450" s="63" t="str">
+        <x:v>SURAJ PRAKASH SAHOO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" ht="15" hidden="0" customHeight="1">
+      <x:c r="A451" s="61" t="str">
+        <x:v>BECE309L</x:v>
+      </x:c>
+      <x:c r="B451" s="62" t="str">
+        <x:v>Artificial Intelligence and Machine Learning</x:v>
+      </x:c>
+      <x:c r="C451" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D451" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E451" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F451" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G451" s="63" t="str">
+        <x:v>THANIKAISELVAN V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" ht="15" hidden="0" customHeight="1">
+      <x:c r="A452" s="61" t="str">
+        <x:v>BECE310L</x:v>
+      </x:c>
+      <x:c r="B452" s="62" t="str">
+        <x:v>Satellite Communications</x:v>
+      </x:c>
+      <x:c r="C452" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D452" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E452" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F452" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G452" s="63" t="str">
+        <x:v>GAUTAM NARAYAN</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" ht="15" hidden="0" customHeight="1">
+      <x:c r="A453" s="61" t="str">
+        <x:v>BECE310L</x:v>
+      </x:c>
+      <x:c r="B453" s="62" t="str">
+        <x:v>Satellite Communications</x:v>
+      </x:c>
+      <x:c r="C453" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D453" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E453" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F453" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G453" s="63" t="str">
+        <x:v>SANGEETHA N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" ht="15" hidden="0" customHeight="1">
+      <x:c r="A454" s="61" t="str">
+        <x:v>BECE310L</x:v>
+      </x:c>
+      <x:c r="B454" s="62" t="str">
+        <x:v>Satellite Communications</x:v>
+      </x:c>
+      <x:c r="C454" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D454" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E454" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F454" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G454" s="63" t="str">
+        <x:v>JABEENA A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" ht="15" hidden="0" customHeight="1">
+      <x:c r="A455" s="61" t="str">
+        <x:v>BECE311L</x:v>
+      </x:c>
+      <x:c r="B455" s="62" t="str">
+        <x:v>Radar Systems</x:v>
+      </x:c>
+      <x:c r="C455" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D455" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E455" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F455" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G455" s="63" t="str">
+        <x:v>SANDHANA MAHALINGAM M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" ht="15" hidden="0" customHeight="1">
+      <x:c r="A456" s="61" t="str">
+        <x:v>BECE311L</x:v>
+      </x:c>
+      <x:c r="B456" s="62" t="str">
+        <x:v>Radar Systems</x:v>
+      </x:c>
+      <x:c r="C456" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D456" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E456" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F456" s="62" t="str">
+        <x:v>G2+TG2</x:v>
+      </x:c>
+      <x:c r="G456" s="63" t="str">
+        <x:v>SANDHANA MAHALINGAM M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" ht="15" hidden="0" customHeight="1">
+      <x:c r="A457" s="61" t="str">
+        <x:v>BECE312L</x:v>
+      </x:c>
+      <x:c r="B457" s="62" t="str">
+        <x:v>Robotics and Automation</x:v>
+      </x:c>
+      <x:c r="C457" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D457" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E457" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F457" s="62" t="str">
+        <x:v>G1+TG1</x:v>
+      </x:c>
+      <x:c r="G457" s="63" t="str">
+        <x:v>BUDHADITYA BHATTACHARYYA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" ht="15" hidden="0" customHeight="1">
+      <x:c r="A458" s="61" t="str">
+        <x:v>BECE313L</x:v>
+      </x:c>
+      <x:c r="B458" s="62" t="str">
+        <x:v>Information Theory and Coding</x:v>
+      </x:c>
+      <x:c r="C458" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D458" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E458" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F458" s="62" t="str">
+        <x:v>E2+TE2</x:v>
+      </x:c>
+      <x:c r="G458" s="63" t="str">
+        <x:v>PREETHA K.S</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" ht="15" hidden="0" customHeight="1">
+      <x:c r="A459" s="61" t="str">
+        <x:v>BECE313L</x:v>
+      </x:c>
+      <x:c r="B459" s="62" t="str">
+        <x:v>Information Theory and Coding</x:v>
+      </x:c>
+      <x:c r="C459" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D459" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E459" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F459" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G459" s="63" t="str">
+        <x:v>NOOR MOHAMMED V</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" ht="15" hidden="0" customHeight="1">
+      <x:c r="A460" s="61" t="str">
+        <x:v>BECE313L</x:v>
+      </x:c>
+      <x:c r="B460" s="62" t="str">
+        <x:v>Information Theory and Coding</x:v>
+      </x:c>
+      <x:c r="C460" s="62" t="str">
+        <x:v>TH</x:v>
+      </x:c>
+      <x:c r="D460" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E460" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F460" s="62" t="str">
+        <x:v>E1+TE1</x:v>
+      </x:c>
+      <x:c r="G460" s="63" t="str">
+        <x:v>SARAVANAN K</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" ht="15" hidden="0" customHeight="1">
+      <x:c r="A461" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B461" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C461" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D461" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E461" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F461" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G461" s="63" t="str">
+        <x:v>DHANABAL R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" ht="15" hidden="0" customHeight="1">
+      <x:c r="A462" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B462" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C462" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D462" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E462" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F462" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G462" s="63" t="str">
+        <x:v>PADMINI T N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" ht="15" hidden="0" customHeight="1">
+      <x:c r="A463" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B463" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C463" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D463" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E463" s="62" t="str">
+        <x:v>TT206</x:v>
+      </x:c>
+      <x:c r="F463" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G463" s="63" t="str">
+        <x:v>DHANABAL R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" ht="15" hidden="0" customHeight="1">
+      <x:c r="A464" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B464" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C464" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D464" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E464" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F464" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G464" s="63" t="str">
+        <x:v>GERARDINE IMMACULATE MARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" ht="15" hidden="0" customHeight="1">
+      <x:c r="A465" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B465" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C465" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D465" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E465" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F465" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G465" s="63" t="str">
+        <x:v>VIDHYAPATHI C.M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" ht="15" hidden="0" customHeight="1">
+      <x:c r="A466" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B466" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C466" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D466" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E466" s="62" t="str">
+        <x:v>TT302</x:v>
+      </x:c>
+      <x:c r="F466" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G466" s="63" t="str">
+        <x:v>SHANMUGASUNDARAM M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" ht="15" hidden="0" customHeight="1">
+      <x:c r="A467" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B467" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C467" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D467" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E467" s="62" t="str">
+        <x:v>TT303</x:v>
+      </x:c>
+      <x:c r="F467" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G467" s="63" t="str">
+        <x:v>MANISH KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" ht="15" hidden="0" customHeight="1">
+      <x:c r="A468" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B468" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C468" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D468" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E468" s="62" t="str">
+        <x:v>TT205</x:v>
+      </x:c>
+      <x:c r="F468" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G468" s="63" t="str">
+        <x:v>PADMINI T N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" ht="15" hidden="0" customHeight="1">
+      <x:c r="A469" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B469" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C469" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D469" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E469" s="62" t="str">
+        <x:v>TT207</x:v>
+      </x:c>
+      <x:c r="F469" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G469" s="63" t="str">
+        <x:v>GERARDINE IMMACULATE MARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" ht="15" hidden="0" customHeight="1">
+      <x:c r="A470" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B470" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C470" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D470" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E470" s="62" t="str">
+        <x:v>TT208</x:v>
+      </x:c>
+      <x:c r="F470" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G470" s="63" t="str">
+        <x:v>S. SUNDAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" ht="15" hidden="0" customHeight="1">
+      <x:c r="A471" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B471" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C471" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D471" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E471" s="62" t="str">
+        <x:v>TT302</x:v>
+      </x:c>
+      <x:c r="F471" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G471" s="63" t="str">
+        <x:v>SURAJ PRAKASH SAHOO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" ht="15" hidden="0" customHeight="1">
+      <x:c r="A472" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B472" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C472" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D472" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E472" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F472" s="62" t="str">
+        <x:v>D1</x:v>
+      </x:c>
+      <x:c r="G472" s="63" t="str">
+        <x:v>VIDHYAPATHI C.M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" ht="15" hidden="0" customHeight="1">
+      <x:c r="A473" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B473" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C473" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D473" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E473" s="62" t="str">
+        <x:v>TT303</x:v>
+      </x:c>
+      <x:c r="F473" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G473" s="63" t="str">
+        <x:v>JAGANA BIHARI PADHY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" ht="15" hidden="0" customHeight="1">
+      <x:c r="A474" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B474" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C474" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D474" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E474" s="62" t="str">
+        <x:v>TT301</x:v>
+      </x:c>
+      <x:c r="F474" s="62" t="str">
+        <x:v>D2</x:v>
+      </x:c>
+      <x:c r="G474" s="63" t="str">
+        <x:v>ELAKKIYA P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" ht="15" hidden="0" customHeight="1">
+      <x:c r="A475" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B475" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C475" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D475" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E475" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F475" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G475" s="63" t="str">
+        <x:v>S. SUNDAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" ht="15" hidden="0" customHeight="1">
+      <x:c r="A476" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B476" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C476" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D476" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E476" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F476" s="62" t="str">
+        <x:v>L39+L40</x:v>
+      </x:c>
+      <x:c r="G476" s="63" t="str">
+        <x:v>PADMINI T N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" ht="15" hidden="0" customHeight="1">
+      <x:c r="A477" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B477" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C477" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D477" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E477" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F477" s="62" t="str">
+        <x:v>L31+L32</x:v>
+      </x:c>
+      <x:c r="G477" s="63" t="str">
+        <x:v>S. SUNDAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" ht="15" hidden="0" customHeight="1">
+      <x:c r="A478" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B478" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C478" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D478" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E478" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F478" s="62" t="str">
+        <x:v>L57+L58</x:v>
+      </x:c>
+      <x:c r="G478" s="63" t="str">
+        <x:v>PADMINI T N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" ht="15" hidden="0" customHeight="1">
+      <x:c r="A479" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B479" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C479" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D479" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E479" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F479" s="62" t="str">
+        <x:v>L27+L28</x:v>
+      </x:c>
+      <x:c r="G479" s="63" t="str">
+        <x:v>DHANABAL R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" ht="15" hidden="0" customHeight="1">
+      <x:c r="A480" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B480" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C480" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D480" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E480" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F480" s="62" t="str">
+        <x:v>L13+L14</x:v>
+      </x:c>
+      <x:c r="G480" s="63" t="str">
+        <x:v>GERARDINE IMMACULATE MARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" ht="15" hidden="0" customHeight="1">
+      <x:c r="A481" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B481" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C481" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D481" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E481" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F481" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G481" s="63" t="str">
+        <x:v>PADMINI T N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" ht="15" hidden="0" customHeight="1">
+      <x:c r="A482" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B482" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C482" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D482" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E482" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F482" s="62" t="str">
+        <x:v>L29+L30</x:v>
+      </x:c>
+      <x:c r="G482" s="63" t="str">
+        <x:v>PADMINI T N</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" ht="15" hidden="0" customHeight="1">
+      <x:c r="A483" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B483" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C483" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D483" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E483" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F483" s="62" t="str">
+        <x:v>L55+L56</x:v>
+      </x:c>
+      <x:c r="G483" s="63" t="str">
+        <x:v>DHANABAL R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" ht="15" hidden="0" customHeight="1">
+      <x:c r="A484" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B484" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C484" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D484" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E484" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F484" s="62" t="str">
+        <x:v>L11+L12</x:v>
+      </x:c>
+      <x:c r="G484" s="63" t="str">
+        <x:v>GERARDINE IMMACULATE MARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" ht="15" hidden="0" customHeight="1">
+      <x:c r="A485" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B485" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C485" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D485" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E485" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F485" s="62" t="str">
+        <x:v>L43+L44</x:v>
+      </x:c>
+      <x:c r="G485" s="63" t="str">
+        <x:v>GERARDINE IMMACULATE MARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" ht="15" hidden="0" customHeight="1">
+      <x:c r="A486" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B486" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C486" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D486" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E486" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F486" s="62" t="str">
+        <x:v>L7+L8</x:v>
+      </x:c>
+      <x:c r="G486" s="63" t="str">
+        <x:v>DHANABAL R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" ht="15" hidden="0" customHeight="1">
+      <x:c r="A487" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B487" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C487" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D487" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E487" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F487" s="62" t="str">
+        <x:v>L37+L38</x:v>
+      </x:c>
+      <x:c r="G487" s="63" t="str">
+        <x:v>DHANABAL R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" ht="15" hidden="0" customHeight="1">
+      <x:c r="A488" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B488" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C488" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D488" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E488" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F488" s="62" t="str">
+        <x:v>L51+L52</x:v>
+      </x:c>
+      <x:c r="G488" s="63" t="str">
+        <x:v>GERARDINE IMMACULATE MARY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" ht="15" hidden="0" customHeight="1">
+      <x:c r="A489" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B489" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C489" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D489" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E489" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F489" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G489" s="63" t="str">
+        <x:v>VIDHYAPATHI C.M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" ht="15" hidden="0" customHeight="1">
+      <x:c r="A490" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B490" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C490" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D490" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E490" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F490" s="62" t="str">
+        <x:v>L25+L26</x:v>
+      </x:c>
+      <x:c r="G490" s="63" t="str">
+        <x:v>VIDHYAPATHI C.M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" ht="15" hidden="0" customHeight="1">
+      <x:c r="A491" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B491" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C491" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D491" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E491" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F491" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G491" s="63" t="str">
+        <x:v>VIDHYAPATHI C.M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" ht="15" hidden="0" customHeight="1">
+      <x:c r="A492" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B492" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C492" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D492" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E492" s="62" t="str">
+        <x:v>TT603</x:v>
+      </x:c>
+      <x:c r="F492" s="62" t="str">
+        <x:v>L35+L36</x:v>
+      </x:c>
+      <x:c r="G492" s="63" t="str">
+        <x:v>VIDHYAPATHI C.M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" ht="15" hidden="0" customHeight="1">
+      <x:c r="A493" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B493" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C493" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D493" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E493" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F493" s="62" t="str">
+        <x:v>L45+L46</x:v>
+      </x:c>
+      <x:c r="G493" s="63" t="str">
+        <x:v>SHANMUGASUNDARAM M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" ht="15" hidden="0" customHeight="1">
+      <x:c r="A494" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B494" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C494" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D494" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E494" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F494" s="62" t="str">
+        <x:v>L41+L42</x:v>
+      </x:c>
+      <x:c r="G494" s="63" t="str">
+        <x:v>SHANMUGASUNDARAM M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" ht="15" hidden="0" customHeight="1">
+      <x:c r="A495" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B495" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C495" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D495" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E495" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F495" s="62" t="str">
+        <x:v>L29+L30</x:v>
+      </x:c>
+      <x:c r="G495" s="63" t="str">
+        <x:v>ELAKKIYA P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" ht="15" hidden="0" customHeight="1">
+      <x:c r="A496" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B496" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C496" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D496" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E496" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F496" s="62" t="str">
+        <x:v>L1+L2</x:v>
+      </x:c>
+      <x:c r="G496" s="63" t="str">
+        <x:v>JAGANA BIHARI PADHY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" ht="15" hidden="0" customHeight="1">
+      <x:c r="A497" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B497" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C497" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D497" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E497" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F497" s="62" t="str">
+        <x:v>L15+L16</x:v>
+      </x:c>
+      <x:c r="G497" s="63" t="str">
+        <x:v>ELAKKIYA P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" ht="15" hidden="0" customHeight="1">
+      <x:c r="A498" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B498" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C498" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D498" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E498" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F498" s="62" t="str">
+        <x:v>L33+L34</x:v>
+      </x:c>
+      <x:c r="G498" s="63" t="str">
+        <x:v>MANISH KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" ht="15" hidden="0" customHeight="1">
+      <x:c r="A499" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B499" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C499" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D499" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E499" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F499" s="62" t="str">
+        <x:v>L5+L6</x:v>
+      </x:c>
+      <x:c r="G499" s="63" t="str">
+        <x:v>SURAJ PRAKASH SAHOO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" ht="15" hidden="0" customHeight="1">
+      <x:c r="A500" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B500" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C500" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D500" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E500" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F500" s="62" t="str">
+        <x:v>L21+L22</x:v>
+      </x:c>
+      <x:c r="G500" s="63" t="str">
+        <x:v>SURAJ PRAKASH SAHOO</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" ht="15" hidden="0" customHeight="1">
+      <x:c r="A501" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B501" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C501" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D501" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E501" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F501" s="62" t="str">
+        <x:v>L49+L50</x:v>
+      </x:c>
+      <x:c r="G501" s="63" t="str">
+        <x:v>MANISH KUMAR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" ht="15" hidden="0" customHeight="1">
+      <x:c r="A502" s="61" t="str">
+        <x:v>BECE320E</x:v>
+      </x:c>
+      <x:c r="B502" s="62" t="str">
+        <x:v>Embedded C Programming</x:v>
+      </x:c>
+      <x:c r="C502" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D502" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E502" s="62" t="str">
+        <x:v>TT729</x:v>
+      </x:c>
+      <x:c r="F502" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G502" s="63" t="str">
+        <x:v>JAGANA BIHARI PADHY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" ht="15" hidden="0" customHeight="1">
+      <x:c r="A503" s="61" t="str">
+        <x:v>BECE403E</x:v>
+      </x:c>
+      <x:c r="B503" s="62" t="str">
+        <x:v>Embedded Systems Design</x:v>
+      </x:c>
+      <x:c r="C503" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D503" s="107" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E503" s="62" t="str">
+        <x:v>TT302</x:v>
+      </x:c>
+      <x:c r="F503" s="62" t="str">
+        <x:v>G2+TG2</x:v>
+      </x:c>
+      <x:c r="G503" s="63" t="str">
+        <x:v>SHABEEB AHAMED K P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" ht="15" hidden="0" customHeight="1">
+      <x:c r="A504" s="61" t="str">
+        <x:v>BECE403E</x:v>
+      </x:c>
+      <x:c r="B504" s="62" t="str">
+        <x:v>Embedded Systems Design</x:v>
+      </x:c>
+      <x:c r="C504" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D504" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E504" s="62" t="str">
+        <x:v>TT601</x:v>
+      </x:c>
+      <x:c r="F504" s="62" t="str">
+        <x:v>L7+L8</x:v>
+      </x:c>
+      <x:c r="G504" s="63" t="str">
+        <x:v>SHABEEB AHAMED K P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" ht="15" hidden="0" customHeight="1">
+      <x:c r="A505" s="61" t="str">
+        <x:v>BECE403E</x:v>
+      </x:c>
+      <x:c r="B505" s="62" t="str">
+        <x:v>Embedded Systems Design</x:v>
+      </x:c>
+      <x:c r="C505" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D505" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E505" s="62" t="str">
+        <x:v>TT601</x:v>
+      </x:c>
+      <x:c r="F505" s="62" t="str">
+        <x:v>L27+L28</x:v>
+      </x:c>
+      <x:c r="G505" s="63" t="str">
+        <x:v>SHABEEB AHAMED K P</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" ht="15" hidden="0" customHeight="1">
+      <x:c r="A506" s="61" t="str">
+        <x:v>BECE407E</x:v>
+      </x:c>
+      <x:c r="B506" s="62" t="str">
+        <x:v>ASIC Design</x:v>
+      </x:c>
+      <x:c r="C506" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D506" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E506" s="62" t="str">
+        <x:v>TT630</x:v>
+      </x:c>
+      <x:c r="F506" s="62" t="str">
+        <x:v>E2</x:v>
+      </x:c>
+      <x:c r="G506" s="63" t="str">
+        <x:v>RAGUNATH G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" ht="15" hidden="0" customHeight="1">
+      <x:c r="A507" s="61" t="str">
+        <x:v>BECE407E</x:v>
+      </x:c>
+      <x:c r="B507" s="62" t="str">
+        <x:v>ASIC Design</x:v>
+      </x:c>
+      <x:c r="C507" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D507" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E507" s="62" t="str">
+        <x:v>TT237A</x:v>
+      </x:c>
+      <x:c r="F507" s="62" t="str">
+        <x:v>L5+L6</x:v>
+      </x:c>
+      <x:c r="G507" s="63" t="str">
+        <x:v>RAGUNATH G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" ht="15" hidden="0" customHeight="1">
+      <x:c r="A508" s="61" t="str">
+        <x:v>BECE407E</x:v>
+      </x:c>
+      <x:c r="B508" s="62" t="str">
+        <x:v>ASIC Design</x:v>
+      </x:c>
+      <x:c r="C508" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D508" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E508" s="62" t="str">
+        <x:v>TT237A</x:v>
+      </x:c>
+      <x:c r="F508" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G508" s="63" t="str">
+        <x:v>RAGUNATH G</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" ht="15" hidden="0" customHeight="1">
+      <x:c r="A509" s="61" t="str">
+        <x:v>BECE409E</x:v>
+      </x:c>
+      <x:c r="B509" s="62" t="str">
+        <x:v>Sensors Technology</x:v>
+      </x:c>
+      <x:c r="C509" s="62" t="str">
+        <x:v>ETH</x:v>
+      </x:c>
+      <x:c r="D509" s="107" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E509" s="62" t="str">
+        <x:v>TT303</x:v>
+      </x:c>
+      <x:c r="F509" s="62" t="str">
+        <x:v>G2</x:v>
+      </x:c>
+      <x:c r="G509" s="63" t="str">
+        <x:v>PRADHEEP T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" ht="15" hidden="0" customHeight="1">
+      <x:c r="A510" s="61" t="str">
+        <x:v>BECE409E</x:v>
+      </x:c>
+      <x:c r="B510" s="62" t="str">
+        <x:v>Sensors Technology</x:v>
+      </x:c>
+      <x:c r="C510" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D510" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E510" s="62" t="str">
+        <x:v>TT503</x:v>
+      </x:c>
+      <x:c r="F510" s="62" t="str">
+        <x:v>L9+L10</x:v>
+      </x:c>
+      <x:c r="G510" s="63" t="str">
+        <x:v>PRADHEEP T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" ht="15" hidden="0" customHeight="1">
+      <x:c r="A511" s="61" t="str">
+        <x:v>BECE409E</x:v>
+      </x:c>
+      <x:c r="B511" s="62" t="str">
+        <x:v>Sensors Technology</x:v>
+      </x:c>
+      <x:c r="C511" s="62" t="str">
+        <x:v>ELA</x:v>
+      </x:c>
+      <x:c r="D511" s="107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E511" s="62" t="str">
+        <x:v>TT503</x:v>
+      </x:c>
+      <x:c r="F511" s="62" t="str">
+        <x:v>L21+L22</x:v>
+      </x:c>
+      <x:c r="G511" s="63" t="str">
+        <x:v>PRADHEEP T</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" ht="15" hidden="0" customHeight="1">
+      <x:c r="A512" s="61" t="str">
+        <x:v>BECE498J</x:v>
+      </x:c>
+      <x:c r="B512" s="62" t="str">
+        <x:v>Project - II / Internship</x:v>
+      </x:c>
+      <x:c r="C512" s="62" t="str">
+        <x:v>PJT</x:v>
+      </x:c>
+      <x:c r="D512" s="107" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E512" s="62" t="str">
+        <x:v>NIL</x:v>
+      </x:c>
+      <x:c r="F512" s="62" t="str">
+        <x:v>NIL</x:v>
+      </x:c>
+      <x:c r="G512" s="63" t="str">
+        <x:v>ACADEMICS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" ht="15" hidden="0" customHeight="1">
+      <x:c r="A513" s="61" t="str">
+        <x:v>BECE498J</x:v>
+      </x:c>
+      <x:c r="B513" s="62" t="str">
+        <x:v>Project - II / Internship</x:v>
+      </x:c>
+      <x:c r="C513" s="62" t="str">
+        <x:v>PJT</x:v>
+      </x:c>
+      <x:c r="D513" s="107" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E513" s="62" t="str">
+        <x:v>NIL</x:v>
+      </x:c>
+      <x:c r="F513" s="62" t="str">
+        <x:v>NIL</x:v>
+      </x:c>
+      <x:c r="G513" s="63" t="str">
+        <x:v>PLACEMENT AND TRAINING</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0c54b304b574bec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf031170480c2422b"/>
   </x:tableParts>
 </x:worksheet>
 </file>